--- a/data/trending_integrated_20260921_10.xlsx
+++ b/data/trending_integrated_20260921_10.xlsx
@@ -567,24 +567,24 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>23000</v>
+        <v>23150</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>'+18.31%</t>
+          <t>'+19.08%</t>
         </is>
       </c>
       <c r="D2" t="n">
         <v>-0.04</v>
       </c>
       <c r="E2" t="n">
-        <v>64</v>
+        <v>74</v>
       </c>
       <c r="F2" t="n">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="G2" t="n">
-        <v>106</v>
+        <v>127</v>
       </c>
       <c r="H2" t="n">
         <v>0.35</v>
@@ -601,7 +601,7 @@
         <v>20200</v>
       </c>
       <c r="L2" t="n">
-        <v>23400</v>
+        <v>24050</v>
       </c>
       <c r="M2" t="n">
         <v>19610</v>
@@ -610,7 +610,7 @@
         <v>0.39</v>
       </c>
       <c r="O2" t="n">
-        <v>104646128535</v>
+        <v>126203725260</v>
       </c>
       <c r="P2" t="n">
         <v>39350</v>
@@ -626,16 +626,16 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>美 타임지 선정 '세계 최고 헬스테크 기업' 선정 소식 기반 급등 후 조정. 글로벌 빅테크 탐색 및 긍정적 전망.</t>
+          <t>美 타임 선정 '세계 최고 헬스테크 기업' 그룹 선정 소식. 주가 급락 후 반등 기대.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>['헬스테크', '타임지', '빅테크']</t>
+          <t>['헬스테크', '타임', '선정']</t>
         </is>
       </c>
       <c r="X2" t="n">
@@ -659,21 +659,21 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>11360</v>
+        <v>11250</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+7.98%</t>
+          <t>'+6.94%</t>
         </is>
       </c>
       <c r="D3" t="n">
         <v>0.16</v>
       </c>
       <c r="E3" t="n">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="F3" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G3" t="n">
         <v>111</v>
@@ -702,7 +702,7 @@
         <v>18.13</v>
       </c>
       <c r="O3" t="n">
-        <v>144896517385</v>
+        <v>150230359655</v>
       </c>
       <c r="P3" t="n">
         <v>22450</v>
@@ -718,16 +718,16 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>광통신 섹터 전반의 긍정적 흐름 속 개인의 섣부른 추격 매수 경계. 일부 투자자는 단기 수익 실현.</t>
+          <t>미국 광통신주 급등에 따른 기대감 반영. 추격 매수 시 주의 요구.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>['광통신', '추격매수', '수익실현']</t>
+          <t>['광통신', '급등', '추격매수']</t>
         </is>
       </c>
       <c r="X3" t="n">
@@ -747,70 +747,70 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>HLB</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>270000</v>
+        <v>31250</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+3.45%</t>
+          <t>'+5.40%</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>-0.02</v>
+        <v>-0.48</v>
       </c>
       <c r="E4" t="n">
-        <v>571</v>
+        <v>103</v>
       </c>
       <c r="F4" t="n">
-        <v>380</v>
+        <v>82</v>
       </c>
       <c r="G4" t="n">
-        <v>2436</v>
+        <v>713</v>
       </c>
       <c r="H4" t="n">
-        <v>46.46</v>
+        <v>16.67</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J4" t="n">
-        <v>261000</v>
+        <v>29650</v>
       </c>
       <c r="K4" t="n">
-        <v>264000</v>
+        <v>30400</v>
       </c>
       <c r="L4" t="n">
-        <v>271500</v>
+        <v>32550</v>
       </c>
       <c r="M4" t="n">
-        <v>263500</v>
+        <v>29400</v>
       </c>
       <c r="N4" t="n">
-        <v>46.48</v>
+        <v>17.15</v>
       </c>
       <c r="O4" t="n">
-        <v>1708766143250</v>
+        <v>9015486525</v>
       </c>
       <c r="P4" t="n">
-        <v>374500</v>
+        <v>69200</v>
       </c>
       <c r="Q4" t="n">
-        <v>81100</v>
+        <v>24150</v>
       </c>
       <c r="R4" t="n">
-        <v>2588000</v>
+        <v>-37000</v>
       </c>
       <c r="S4" t="n">
-        <v>189000</v>
+        <v>-1000</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>AI 감속론 반박 및 배당 기대감 속 상승 전망. 일부 투자자는 증권사 전산 오류에 대한 불만을 제기.</t>
+          <t>FDA 승인 기대감과 신약 개발 관련 논의가 있으나, 과거 실패 사례와 손실 중인 투자자들의 경고도 나타남.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
@@ -819,11 +819,11 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['AI', '배당', '상승전망']</t>
+          <t>['FDA 승인', '신약 개발', '임상']</t>
         </is>
       </c>
       <c r="X4" t="n">
-        <v>110</v>
+        <v>1</v>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
@@ -832,77 +832,77 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>005930</t>
+          <t>028300</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>HLB</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>30300</v>
+        <v>270750</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+2.19%</t>
+          <t>'+3.74%</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>-0.48</v>
+        <v>-0.02</v>
       </c>
       <c r="E5" t="n">
-        <v>97</v>
+        <v>598</v>
       </c>
       <c r="F5" t="n">
-        <v>76</v>
+        <v>390</v>
       </c>
       <c r="G5" t="n">
-        <v>685</v>
+        <v>2538</v>
       </c>
       <c r="H5" t="n">
-        <v>16.67</v>
+        <v>46.46</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J5" t="n">
-        <v>29650</v>
+        <v>261000</v>
       </c>
       <c r="K5" t="n">
-        <v>30400</v>
+        <v>264000</v>
       </c>
       <c r="L5" t="n">
-        <v>30400</v>
+        <v>271500</v>
       </c>
       <c r="M5" t="n">
-        <v>29400</v>
+        <v>263500</v>
       </c>
       <c r="N5" t="n">
-        <v>17.15</v>
+        <v>46.48</v>
       </c>
       <c r="O5" t="n">
-        <v>4385096250</v>
+        <v>1899846846750</v>
       </c>
       <c r="P5" t="n">
-        <v>69200</v>
+        <v>374500</v>
       </c>
       <c r="Q5" t="n">
-        <v>24150</v>
+        <v>81100</v>
       </c>
       <c r="R5" t="n">
-        <v>-37000</v>
+        <v>2588000</v>
       </c>
       <c r="S5" t="n">
-        <v>-1000</v>
+        <v>189000</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>FDA 승인 관련 기대감 속에서도 실패 가능성 및 회사 입장 정리 필요성 제기. 투자자 손실 우려.</t>
+          <t>AI 감속론 부인 및 배당 기대감으로 인한 상승 전망. 신한증권 시스템 오류에 대한 불만 제기.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
@@ -911,11 +911,11 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['FDA승인', '담관암', '손실우려']</t>
+          <t>['AI', '배당', '상승장']</t>
         </is>
       </c>
       <c r="X5" t="n">
-        <v>1</v>
+        <v>110</v>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
@@ -924,7 +924,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>028300</t>
+          <t>005930</t>
         </is>
       </c>
     </row>
@@ -935,24 +935,24 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1869500</v>
+        <v>1878000</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'+0.67%</t>
+          <t>'+1.13%</t>
         </is>
       </c>
       <c r="D6" t="n">
         <v>0.13</v>
       </c>
       <c r="E6" t="n">
-        <v>651</v>
+        <v>671</v>
       </c>
       <c r="F6" t="n">
-        <v>397</v>
+        <v>405</v>
       </c>
       <c r="G6" t="n">
-        <v>2646</v>
+        <v>2706</v>
       </c>
       <c r="H6" t="n">
         <v>50.23</v>
@@ -978,7 +978,7 @@
         <v>50.1</v>
       </c>
       <c r="O6" t="n">
-        <v>1408934595000</v>
+        <v>1573599410500</v>
       </c>
       <c r="P6" t="n">
         <v>2987000</v>
@@ -994,16 +994,16 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>HBM 수율 문제에도 불구, 반도체 시장 성장 및 수출 호조 전망. 외인 매수세 유입 및 200만닉스 돌파 기대.</t>
+          <t>HBM 수율 관련 부정적 뉴스에도 불구하고 반도체 시장 성장 전망. AI 속도 조절론 무색.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>0.6</v>
+        <v>0.3</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['HBM', '반도체', '수출']</t>
+          <t>['HBM', '반도체', 'AI']</t>
         </is>
       </c>
       <c r="X6" t="n">
@@ -1027,24 +1027,24 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4230</v>
+        <v>4180</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'+0.24%</t>
+          <t>'-0.95%</t>
         </is>
       </c>
       <c r="D7" t="n">
         <v>-0.22</v>
       </c>
       <c r="E7" t="n">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="F7" t="n">
         <v>30</v>
       </c>
       <c r="G7" t="n">
-        <v>108</v>
+        <v>121</v>
       </c>
       <c r="H7" t="n">
         <v>0.33</v>
@@ -1064,13 +1064,13 @@
         <v>4415</v>
       </c>
       <c r="M7" t="n">
-        <v>4180</v>
+        <v>4170</v>
       </c>
       <c r="N7" t="n">
         <v>0.55</v>
       </c>
       <c r="O7" t="n">
-        <v>21996504271</v>
+        <v>23444430350</v>
       </c>
       <c r="P7" t="n">
         <v>6480</v>
@@ -1086,16 +1086,16 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>미버스 코인 관련 상승세 및 STO 사업 기대감. 다만 거래량 부족 및 주가 힘 없음 지적.</t>
+          <t>미버스 코인 급등에도 불구하고 본주 거래량 부진 및 매도 압력 언급. 다른 관련주 대비 부진.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['미버스', 'STO', '거래량']</t>
+          <t>['미버스', '코인', '거래량']</t>
         </is>
       </c>
       <c r="X7" t="n">
@@ -1119,24 +1119,24 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>17770</v>
+        <v>17800</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'-3.00%</t>
+          <t>'-2.84%</t>
         </is>
       </c>
       <c r="D8" t="n">
         <v>3.29</v>
       </c>
       <c r="E8" t="n">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="F8" t="n">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="G8" t="n">
-        <v>634</v>
+        <v>663</v>
       </c>
       <c r="H8" t="n">
         <v>7.9</v>
@@ -1162,7 +1162,7 @@
         <v>4.61</v>
       </c>
       <c r="O8" t="n">
-        <v>137964209430</v>
+        <v>143070483120</v>
       </c>
       <c r="P8" t="n">
         <v>31500</v>
@@ -1178,16 +1178,16 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>미국 광통신주 급등 및 AI 관련 호재에 따른 상승 기대감. 기관 및 외국인 수급 긍정적 전망.</t>
+          <t>미국 광통신주 급등에 따른 기대감 반영. 기관 매수 및 연말까지 상승 전망.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="n">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>['광통신', 'AI', '외국인수급']</t>
+          <t>['광통신', '기관', '상승']</t>
         </is>
       </c>
       <c r="X8" t="n">
@@ -1207,31 +1207,31 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>대우건설</t>
+          <t>한화시스템</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>18220</v>
+        <v>77400</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>'-3.65%</t>
+          <t>'-3.25%</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>0</v>
+        <v>-0.1</v>
       </c>
       <c r="E9" t="n">
-        <v>41</v>
+        <v>109</v>
       </c>
       <c r="F9" t="n">
-        <v>31</v>
+        <v>67</v>
       </c>
       <c r="G9" t="n">
-        <v>168</v>
+        <v>457</v>
       </c>
       <c r="H9" t="n">
-        <v>10.74</v>
+        <v>10.58</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -1239,51 +1239,51 @@
         </is>
       </c>
       <c r="J9" t="n">
-        <v>18910</v>
+        <v>80000</v>
       </c>
       <c r="K9" t="n">
-        <v>19050</v>
+        <v>82900</v>
       </c>
       <c r="L9" t="n">
-        <v>19050</v>
+        <v>83000</v>
       </c>
       <c r="M9" t="n">
-        <v>18090</v>
+        <v>75300</v>
       </c>
       <c r="N9" t="n">
-        <v>10.74</v>
+        <v>10.68</v>
       </c>
       <c r="O9" t="n">
-        <v>39803913450</v>
+        <v>68883631500</v>
       </c>
       <c r="P9" t="n">
-        <v>40350</v>
+        <v>184000</v>
       </c>
       <c r="Q9" t="n">
-        <v>3320</v>
+        <v>44750</v>
       </c>
       <c r="R9" t="n">
-        <v>-331000</v>
+        <v>-324000</v>
       </c>
       <c r="S9" t="n">
-        <v>-47000</v>
+        <v>-60000</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>공매도 세력과의 갈등 속 대차 해지 운동 참여 독려. 주가 하락에 대한 불만 표출.</t>
+          <t>K-방산 관련 뉴스에 따른 기대감. 공매도 청산 및 주가 상승 전망.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['공매도', '대차해지', '주가하락']</t>
+          <t>['K-방산', '공매도', '주가 상승']</t>
         </is>
       </c>
       <c r="X9" t="n">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
@@ -1292,38 +1292,38 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>047040</t>
+          <t>272210</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>한화시스템</t>
+          <t>대한전선</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>76900</v>
+        <v>30400</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'-3.88%</t>
+          <t>'-3.34%</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>-0.1</v>
+        <v>0.48</v>
       </c>
       <c r="E10" t="n">
-        <v>98</v>
+        <v>57</v>
       </c>
       <c r="F10" t="n">
-        <v>62</v>
+        <v>36</v>
       </c>
       <c r="G10" t="n">
-        <v>422</v>
+        <v>100</v>
       </c>
       <c r="H10" t="n">
-        <v>10.58</v>
+        <v>11.92</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -1331,51 +1331,51 @@
         </is>
       </c>
       <c r="J10" t="n">
-        <v>80000</v>
+        <v>31450</v>
       </c>
       <c r="K10" t="n">
-        <v>82900</v>
+        <v>31500</v>
       </c>
       <c r="L10" t="n">
-        <v>83000</v>
+        <v>31550</v>
       </c>
       <c r="M10" t="n">
-        <v>75300</v>
+        <v>29950</v>
       </c>
       <c r="N10" t="n">
-        <v>10.68</v>
+        <v>11.44</v>
       </c>
       <c r="O10" t="n">
-        <v>65716691950</v>
+        <v>52563657375</v>
       </c>
       <c r="P10" t="n">
-        <v>184000</v>
+        <v>75900</v>
       </c>
       <c r="Q10" t="n">
-        <v>44750</v>
+        <v>15000</v>
       </c>
       <c r="R10" t="n">
-        <v>-324000</v>
+        <v>-166000</v>
       </c>
       <c r="S10" t="n">
-        <v>-60000</v>
+        <v>-8000</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>K-방산 관련 긍정적 뉴스 언급 및 공매도 청산 기대감. 일부는 매물대 돌파 후 상승 전망.</t>
+          <t>개인 투자자의 대한전선 매도 및 전선주 하락세 언급. 수급 불균형 우려.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="n">
-        <v>0.3</v>
+        <v>0.1</v>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>['K-방산', '공매도', '매물대']</t>
+          <t>['전선주', '매도', '수급']</t>
         </is>
       </c>
       <c r="X10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
@@ -1384,38 +1384,38 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>272210</t>
+          <t>001440</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>가온전선</t>
+          <t>대우건설</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>313000</v>
+        <v>18220</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>'-4.28%</t>
+          <t>'-3.65%</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="E11" t="n">
-        <v>83</v>
+        <v>45</v>
       </c>
       <c r="F11" t="n">
-        <v>61</v>
+        <v>33</v>
       </c>
       <c r="G11" t="n">
-        <v>169</v>
+        <v>193</v>
       </c>
       <c r="H11" t="n">
-        <v>3.62</v>
+        <v>10.74</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -1423,51 +1423,51 @@
         </is>
       </c>
       <c r="J11" t="n">
-        <v>327000</v>
+        <v>18910</v>
       </c>
       <c r="K11" t="n">
-        <v>324000</v>
+        <v>19050</v>
       </c>
       <c r="L11" t="n">
-        <v>340500</v>
+        <v>19050</v>
       </c>
       <c r="M11" t="n">
-        <v>312000</v>
+        <v>18090</v>
       </c>
       <c r="N11" t="n">
-        <v>1.96</v>
+        <v>10.74</v>
       </c>
       <c r="O11" t="n">
-        <v>54904214000</v>
+        <v>42205532415</v>
       </c>
       <c r="P11" t="n">
-        <v>635000</v>
+        <v>40350</v>
       </c>
       <c r="Q11" t="n">
-        <v>52600</v>
+        <v>3320</v>
       </c>
       <c r="R11" t="n">
-        <v>-24000</v>
+        <v>-331000</v>
       </c>
       <c r="S11" t="n">
-        <v>-2000</v>
+        <v>-47000</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>가온전선 주가 고평가 논란 및 차익 실현 매물 출회 가능성 제기. 일부는 외국인 수급 긍정적 전망.</t>
+          <t>공매도 장부 조작 및 대차 오링 의혹 제기. 대차해지 운동 참여 독려.</t>
         </is>
       </c>
       <c r="U11" t="inlineStr"/>
       <c r="V11" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>['고평가', '차익실현', '외국인']</t>
+          <t>['공매도', '대차', '주가 조작']</t>
         </is>
       </c>
       <c r="X11" t="n">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
@@ -1476,38 +1476,38 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>000500</t>
+          <t>047040</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>대한전선</t>
+          <t>가온전선</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>30050</v>
+        <v>314500</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>'-4.45%</t>
+          <t>'-3.82%</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>0.48</v>
+        <v>1.66</v>
       </c>
       <c r="E12" t="n">
-        <v>53</v>
+        <v>87</v>
       </c>
       <c r="F12" t="n">
-        <v>33</v>
+        <v>63</v>
       </c>
       <c r="G12" t="n">
-        <v>92</v>
+        <v>167</v>
       </c>
       <c r="H12" t="n">
-        <v>11.92</v>
+        <v>3.62</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -1515,38 +1515,38 @@
         </is>
       </c>
       <c r="J12" t="n">
-        <v>31450</v>
+        <v>327000</v>
       </c>
       <c r="K12" t="n">
-        <v>31500</v>
+        <v>324000</v>
       </c>
       <c r="L12" t="n">
-        <v>31550</v>
+        <v>340500</v>
       </c>
       <c r="M12" t="n">
-        <v>29950</v>
+        <v>308500</v>
       </c>
       <c r="N12" t="n">
-        <v>11.44</v>
+        <v>1.96</v>
       </c>
       <c r="O12" t="n">
-        <v>49835896175</v>
+        <v>61767353250</v>
       </c>
       <c r="P12" t="n">
-        <v>75900</v>
+        <v>635000</v>
       </c>
       <c r="Q12" t="n">
-        <v>15000</v>
+        <v>52600</v>
       </c>
       <c r="R12" t="n">
-        <v>-166000</v>
+        <v>-24000</v>
       </c>
       <c r="S12" t="n">
-        <v>-8000</v>
+        <v>-2000</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>전선주 전반의 약세 속 대한전선 주가 하락에 대한 실망감 표현. 단기 매매 차익 실현 언급.</t>
+          <t>일부 투자자들은 긍정적인 추세와 공급 계약을 언급하지만, 고평가 및 하락 의견도 존재하여 혼조세.</t>
         </is>
       </c>
       <c r="U12" t="inlineStr"/>
@@ -1555,11 +1555,11 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>['전선주', '주가하락', '단기매매']</t>
+          <t>['공급 계약', '고평가', '추세']</t>
         </is>
       </c>
       <c r="X12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
@@ -1568,7 +1568,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>001440</t>
+          <t>000500</t>
         </is>
       </c>
     </row>
@@ -1579,24 +1579,24 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>26900</v>
+        <v>27100</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>'-28.07%</t>
+          <t>'-27.54%</t>
         </is>
       </c>
       <c r="D13" t="n">
         <v>0.01</v>
       </c>
       <c r="E13" t="n">
-        <v>466</v>
+        <v>472</v>
       </c>
       <c r="F13" t="n">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="G13" t="n">
-        <v>915</v>
+        <v>906</v>
       </c>
       <c r="H13" t="n">
         <v>7.09</v>
@@ -1622,7 +1622,7 @@
         <v>7.08</v>
       </c>
       <c r="O13" t="n">
-        <v>58689740975</v>
+        <v>60488955125</v>
       </c>
       <c r="P13" t="n">
         <v>146600</v>
@@ -1638,16 +1638,16 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>하한가 이후 반등 시도했으나, 임상 결과 및 바이오 투기 심리에 대한 부정적 전망. 착한 개미들의 손실 우려.</t>
+          <t>임상 진행 관련 불확실성 및 연속 하한가 발생. 투자자들의 신중한 접근 요구.</t>
         </is>
       </c>
       <c r="U13" t="inlineStr"/>
       <c r="V13" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>['임상', '바이오', '하한가']</t>
+          <t>['임상', '하한가', '바이오']</t>
         </is>
       </c>
       <c r="X13" t="n">

--- a/data/trending_integrated_20260921_10.xlsx
+++ b/data/trending_integrated_20260921_10.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z13"/>
+  <dimension ref="A1:Z16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -567,24 +567,24 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>23150</v>
+        <v>22800</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>'+19.08%</t>
+          <t>'+17.28%</t>
         </is>
       </c>
       <c r="D2" t="n">
         <v>-0.04</v>
       </c>
       <c r="E2" t="n">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="F2" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="G2" t="n">
-        <v>127</v>
+        <v>142</v>
       </c>
       <c r="H2" t="n">
         <v>0.35</v>
@@ -610,7 +610,7 @@
         <v>0.39</v>
       </c>
       <c r="O2" t="n">
-        <v>126203725260</v>
+        <v>133604175585</v>
       </c>
       <c r="P2" t="n">
         <v>39350</v>
@@ -626,16 +626,16 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>美 타임 선정 '세계 최고 헬스테크 기업' 그룹 선정 소식. 주가 급락 후 반등 기대.</t>
+          <t>美 타임 선정 '세계 최고 헬스테크 기업' 선정. 삼성과 4381억 계약 체결 및 5만원 이상 상승 전망.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
-        <v>0.4</v>
+        <v>0.7</v>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>['헬스테크', '타임', '선정']</t>
+          <t>['스카이랩스', '헬스테크', '타임']</t>
         </is>
       </c>
       <c r="X2" t="n">
@@ -655,83 +655,83 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>광전자</t>
+          <t>HLB</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>11250</v>
+        <v>33400</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+6.94%</t>
+          <t>'+12.65%</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>0.16</v>
+        <v>-0.48</v>
       </c>
       <c r="E3" t="n">
-        <v>57</v>
+        <v>144</v>
       </c>
       <c r="F3" t="n">
-        <v>39</v>
+        <v>109</v>
       </c>
       <c r="G3" t="n">
-        <v>111</v>
+        <v>783</v>
       </c>
       <c r="H3" t="n">
-        <v>18.29</v>
+        <v>16.67</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J3" t="n">
-        <v>10520</v>
+        <v>29650</v>
       </c>
       <c r="K3" t="n">
-        <v>10780</v>
+        <v>30400</v>
       </c>
       <c r="L3" t="n">
-        <v>12190</v>
+        <v>33400</v>
       </c>
       <c r="M3" t="n">
-        <v>10590</v>
+        <v>29400</v>
       </c>
       <c r="N3" t="n">
-        <v>18.13</v>
+        <v>17.15</v>
       </c>
       <c r="O3" t="n">
-        <v>150230359655</v>
+        <v>14003134275</v>
       </c>
       <c r="P3" t="n">
-        <v>22450</v>
+        <v>69200</v>
       </c>
       <c r="Q3" t="n">
-        <v>1760</v>
+        <v>24150</v>
       </c>
       <c r="R3" t="n">
-        <v>-18000</v>
+        <v>-37000</v>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>-1000</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>미국 광통신주 급등에 따른 기대감 반영. 추격 매수 시 주의 요구.</t>
+          <t>FDA 승인 관련 기대와 불확실성 혼재. 임상 성공 여부 및 주가 패턴에 대한 논쟁.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>['광통신', '급등', '추격매수']</t>
+          <t>['FDA승인', '임상성공', '주가패턴']</t>
         </is>
       </c>
       <c r="X3" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
@@ -740,38 +740,38 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>017900</t>
+          <t>028300</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>HLB</t>
+          <t>우리기술투자</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>31250</v>
+        <v>6040</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+5.40%</t>
+          <t>'+11.23%</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>-0.48</v>
+        <v>-0.31</v>
       </c>
       <c r="E4" t="n">
-        <v>103</v>
+        <v>41</v>
       </c>
       <c r="F4" t="n">
-        <v>82</v>
+        <v>24</v>
       </c>
       <c r="G4" t="n">
-        <v>713</v>
+        <v>110</v>
       </c>
       <c r="H4" t="n">
-        <v>16.67</v>
+        <v>0.19</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -779,47 +779,47 @@
         </is>
       </c>
       <c r="J4" t="n">
-        <v>29650</v>
+        <v>5430</v>
       </c>
       <c r="K4" t="n">
-        <v>30400</v>
+        <v>5710</v>
       </c>
       <c r="L4" t="n">
-        <v>32550</v>
+        <v>6280</v>
       </c>
       <c r="M4" t="n">
-        <v>29400</v>
+        <v>5600</v>
       </c>
       <c r="N4" t="n">
-        <v>17.15</v>
+        <v>0.5</v>
       </c>
       <c r="O4" t="n">
-        <v>9015486525</v>
+        <v>52605612475</v>
       </c>
       <c r="P4" t="n">
-        <v>69200</v>
+        <v>13140</v>
       </c>
       <c r="Q4" t="n">
-        <v>24150</v>
+        <v>3725</v>
       </c>
       <c r="R4" t="n">
-        <v>-37000</v>
+        <v>-148000</v>
       </c>
       <c r="S4" t="n">
-        <v>-1000</v>
+        <v>0</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>FDA 승인 기대감과 신약 개발 관련 논의가 있으나, 과거 실패 사례와 손실 중인 투자자들의 경고도 나타남.</t>
+          <t>비트코인 81,500달러 돌파에 따른 기대감 상승. 공매도 세력에 대한 부정적 언급 및 매수세 유입.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['FDA 승인', '신약 개발', '임상']</t>
+          <t>['우리기술투자', '비트코인', '공매도']</t>
         </is>
       </c>
       <c r="X4" t="n">
@@ -832,38 +832,38 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>028300</t>
+          <t>041190</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>삼성전자우</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>270750</v>
+        <v>207000</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+3.74%</t>
+          <t>'+5.56%</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>-0.02</v>
+        <v>-0.09</v>
       </c>
       <c r="E5" t="n">
-        <v>598</v>
+        <v>40</v>
       </c>
       <c r="F5" t="n">
-        <v>390</v>
+        <v>34</v>
       </c>
       <c r="G5" t="n">
-        <v>2538</v>
+        <v>175</v>
       </c>
       <c r="H5" t="n">
-        <v>46.46</v>
+        <v>75.44</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -871,51 +871,51 @@
         </is>
       </c>
       <c r="J5" t="n">
-        <v>261000</v>
+        <v>196100</v>
       </c>
       <c r="K5" t="n">
-        <v>264000</v>
+        <v>199800</v>
       </c>
       <c r="L5" t="n">
-        <v>271500</v>
+        <v>207000</v>
       </c>
       <c r="M5" t="n">
-        <v>263500</v>
+        <v>199600</v>
       </c>
       <c r="N5" t="n">
-        <v>46.48</v>
+        <v>75.53</v>
       </c>
       <c r="O5" t="n">
-        <v>1899846846750</v>
+        <v>394884304300</v>
       </c>
       <c r="P5" t="n">
-        <v>374500</v>
+        <v>243500</v>
       </c>
       <c r="Q5" t="n">
-        <v>81100</v>
+        <v>64700</v>
       </c>
       <c r="R5" t="n">
-        <v>2588000</v>
+        <v>398000</v>
       </c>
       <c r="S5" t="n">
-        <v>189000</v>
+        <v>-36000</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>AI 감속론 부인 및 배당 기대감으로 인한 상승 전망. 신한증권 시스템 오류에 대한 불만 제기.</t>
+          <t>배당락 D-4일, 우선주 자사주 취득소각 기대감. 20만원 돌파 및 20만 7천원, 21만원 목표.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>0.2</v>
+        <v>0.5</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['AI', '배당', '상승장']</t>
+          <t>['삼성전자우', '배당', '자사주']</t>
         </is>
       </c>
       <c r="X5" t="n">
-        <v>110</v>
+        <v>1</v>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
@@ -924,38 +924,38 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>005930</t>
+          <t>005935</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>광전자</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1878000</v>
+        <v>11070</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'+1.13%</t>
+          <t>'+5.23%</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>0.13</v>
+        <v>0.16</v>
       </c>
       <c r="E6" t="n">
-        <v>671</v>
+        <v>70</v>
       </c>
       <c r="F6" t="n">
-        <v>405</v>
+        <v>51</v>
       </c>
       <c r="G6" t="n">
-        <v>2706</v>
+        <v>127</v>
       </c>
       <c r="H6" t="n">
-        <v>50.23</v>
+        <v>18.29</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -963,51 +963,51 @@
         </is>
       </c>
       <c r="J6" t="n">
-        <v>1857000</v>
+        <v>10520</v>
       </c>
       <c r="K6" t="n">
-        <v>1872000</v>
+        <v>10780</v>
       </c>
       <c r="L6" t="n">
-        <v>1888000</v>
+        <v>12190</v>
       </c>
       <c r="M6" t="n">
-        <v>1847000</v>
+        <v>10590</v>
       </c>
       <c r="N6" t="n">
-        <v>50.1</v>
+        <v>18.13</v>
       </c>
       <c r="O6" t="n">
-        <v>1573599410500</v>
+        <v>154117913460</v>
       </c>
       <c r="P6" t="n">
-        <v>2987000</v>
+        <v>22450</v>
       </c>
       <c r="Q6" t="n">
-        <v>333000</v>
+        <v>1760</v>
       </c>
       <c r="R6" t="n">
-        <v>-78000</v>
+        <v>-18000</v>
       </c>
       <c r="S6" t="n">
-        <v>55000</v>
+        <v>0</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>HBM 수율 관련 부정적 뉴스에도 불구하고 반도체 시장 성장 전망. AI 속도 조절론 무색.</t>
+          <t>미국 광통신주 급등에 따른 기대감 상승. 하지만 추격 매수 및 투자 주의 언급.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['HBM', '반도체', 'AI']</t>
+          <t>['광통신', '나스닥선물', '추격매수']</t>
         </is>
       </c>
       <c r="X6" t="n">
-        <v>75</v>
+        <v>6</v>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
@@ -1016,90 +1016,90 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>000660</t>
+          <t>017900</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>미투온</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4180</v>
+        <v>271500</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'-0.95%</t>
+          <t>'+4.02%</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>-0.22</v>
+        <v>-0.02</v>
       </c>
       <c r="E7" t="n">
-        <v>51</v>
+        <v>658</v>
       </c>
       <c r="F7" t="n">
-        <v>30</v>
+        <v>426</v>
       </c>
       <c r="G7" t="n">
-        <v>121</v>
+        <v>2655</v>
       </c>
       <c r="H7" t="n">
-        <v>0.33</v>
+        <v>46.46</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J7" t="n">
-        <v>4220</v>
+        <v>261000</v>
       </c>
       <c r="K7" t="n">
-        <v>4220</v>
+        <v>264000</v>
       </c>
       <c r="L7" t="n">
-        <v>4415</v>
+        <v>272000</v>
       </c>
       <c r="M7" t="n">
-        <v>4170</v>
+        <v>263500</v>
       </c>
       <c r="N7" t="n">
-        <v>0.55</v>
+        <v>46.48</v>
       </c>
       <c r="O7" t="n">
-        <v>23444430350</v>
+        <v>2117467782250</v>
       </c>
       <c r="P7" t="n">
-        <v>6480</v>
+        <v>374500</v>
       </c>
       <c r="Q7" t="n">
-        <v>1738</v>
+        <v>81100</v>
       </c>
       <c r="R7" t="n">
-        <v>121000</v>
+        <v>2588000</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>189000</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>미버스 코인 급등에도 불구하고 본주 거래량 부진 및 매도 압력 언급. 다른 관련주 대비 부진.</t>
+          <t>AI 감속론 부인 및 배당 기대감으로 인한 상승 전망. 신한증권 시스템 오류에 대한 불만 제기.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['미버스', '코인', '거래량']</t>
+          <t>['AI', '배당', '상승장']</t>
         </is>
       </c>
       <c r="X7" t="n">
-        <v>4</v>
+        <v>110</v>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
@@ -1108,90 +1108,90 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>201490</t>
+          <t>005930</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>대한광통신</t>
+          <t>SK하이닉스</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>17800</v>
+        <v>1877000</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'-2.84%</t>
+          <t>'+1.08%</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>3.29</v>
+        <v>0.13</v>
       </c>
       <c r="E8" t="n">
-        <v>149</v>
+        <v>711</v>
       </c>
       <c r="F8" t="n">
-        <v>108</v>
+        <v>429</v>
       </c>
       <c r="G8" t="n">
-        <v>663</v>
+        <v>2761</v>
       </c>
       <c r="H8" t="n">
-        <v>7.9</v>
+        <v>50.23</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J8" t="n">
-        <v>18320</v>
+        <v>1857000</v>
       </c>
       <c r="K8" t="n">
-        <v>18450</v>
+        <v>1872000</v>
       </c>
       <c r="L8" t="n">
-        <v>18590</v>
+        <v>1888000</v>
       </c>
       <c r="M8" t="n">
-        <v>17590</v>
+        <v>1847000</v>
       </c>
       <c r="N8" t="n">
-        <v>4.61</v>
+        <v>50.1</v>
       </c>
       <c r="O8" t="n">
-        <v>143070483120</v>
+        <v>1722613367500</v>
       </c>
       <c r="P8" t="n">
-        <v>31500</v>
+        <v>2987000</v>
       </c>
       <c r="Q8" t="n">
-        <v>1272</v>
+        <v>333000</v>
       </c>
       <c r="R8" t="n">
-        <v>-916000</v>
+        <v>-78000</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>55000</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>미국 광통신주 급등에 따른 기대감 반영. 기관 매수 및 연말까지 상승 전망.</t>
+          <t>미국 증시 반도체주 급등 및 HBM 시장 성장 전망. 20만원 돌파 및 분기 사상 최고 영업이익 예상.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="n">
-        <v>0.2</v>
+        <v>0.6</v>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>['광통신', '기관', '상승']</t>
+          <t>['SK하이닉스', 'HBM', '반도체']</t>
         </is>
       </c>
       <c r="X8" t="n">
-        <v>19</v>
+        <v>75</v>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
@@ -1200,77 +1200,77 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>010170</t>
+          <t>000660</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>한화시스템</t>
+          <t>우리기술</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>77400</v>
+        <v>13870</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>'-3.25%</t>
+          <t>'+0.00%</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>-0.1</v>
+        <v>0.58</v>
       </c>
       <c r="E9" t="n">
-        <v>109</v>
+        <v>41</v>
       </c>
       <c r="F9" t="n">
-        <v>67</v>
+        <v>24</v>
       </c>
       <c r="G9" t="n">
-        <v>457</v>
+        <v>212</v>
       </c>
       <c r="H9" t="n">
-        <v>10.58</v>
+        <v>5.5</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J9" t="n">
-        <v>80000</v>
+        <v>13870</v>
       </c>
       <c r="K9" t="n">
-        <v>82900</v>
+        <v>14070</v>
       </c>
       <c r="L9" t="n">
-        <v>83000</v>
+        <v>14790</v>
       </c>
       <c r="M9" t="n">
-        <v>75300</v>
+        <v>13760</v>
       </c>
       <c r="N9" t="n">
-        <v>10.68</v>
+        <v>4.92</v>
       </c>
       <c r="O9" t="n">
-        <v>68883631500</v>
+        <v>49925552850</v>
       </c>
       <c r="P9" t="n">
-        <v>184000</v>
+        <v>30200</v>
       </c>
       <c r="Q9" t="n">
-        <v>44750</v>
+        <v>3540</v>
       </c>
       <c r="R9" t="n">
-        <v>-324000</v>
+        <v>-179000</v>
       </c>
       <c r="S9" t="n">
-        <v>-60000</v>
+        <v>-3000</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>K-방산 관련 뉴스에 따른 기대감. 공매도 청산 및 주가 상승 전망.</t>
+          <t>미 증권가 원전 관련 긍정적 전망. 신용 증가 및 프로그램 매매 동향 언급.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
@@ -1279,11 +1279,11 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['K-방산', '공매도', '주가 상승']</t>
+          <t>['우리기술', '원전', '프로그램']</t>
         </is>
       </c>
       <c r="X9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
@@ -1292,90 +1292,90 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>272210</t>
+          <t>032820</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>대한전선</t>
+          <t>미투온</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>30400</v>
+        <v>4185</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'-3.34%</t>
+          <t>'-0.83%</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>0.48</v>
+        <v>-0.22</v>
       </c>
       <c r="E10" t="n">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="F10" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G10" t="n">
-        <v>100</v>
+        <v>135</v>
       </c>
       <c r="H10" t="n">
-        <v>11.92</v>
+        <v>0.33</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J10" t="n">
-        <v>31450</v>
+        <v>4220</v>
       </c>
       <c r="K10" t="n">
-        <v>31500</v>
+        <v>4220</v>
       </c>
       <c r="L10" t="n">
-        <v>31550</v>
+        <v>4415</v>
       </c>
       <c r="M10" t="n">
-        <v>29950</v>
+        <v>4125</v>
       </c>
       <c r="N10" t="n">
-        <v>11.44</v>
+        <v>0.55</v>
       </c>
       <c r="O10" t="n">
-        <v>52563657375</v>
+        <v>24572543174</v>
       </c>
       <c r="P10" t="n">
-        <v>75900</v>
+        <v>6480</v>
       </c>
       <c r="Q10" t="n">
-        <v>15000</v>
+        <v>1738</v>
       </c>
       <c r="R10" t="n">
-        <v>-166000</v>
+        <v>121000</v>
       </c>
       <c r="S10" t="n">
-        <v>-8000</v>
+        <v>0</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>개인 투자자의 대한전선 매도 및 전선주 하락세 언급. 수급 불균형 우려.</t>
+          <t>코인 관련주 및 미버스 급등 속 상대적 부진. 거래량 부족 및 매도 폭탄 언급.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>['전선주', '매도', '수급']</t>
+          <t>['미투온', '코인', '미버스']</t>
         </is>
       </c>
       <c r="X10" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
@@ -1384,38 +1384,38 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>001440</t>
+          <t>201490</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>대우건설</t>
+          <t>한화시스템</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>18220</v>
+        <v>79000</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>'-3.65%</t>
+          <t>'-1.25%</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>0</v>
+        <v>-0.1</v>
       </c>
       <c r="E11" t="n">
-        <v>45</v>
+        <v>115</v>
       </c>
       <c r="F11" t="n">
-        <v>33</v>
+        <v>69</v>
       </c>
       <c r="G11" t="n">
-        <v>193</v>
+        <v>471</v>
       </c>
       <c r="H11" t="n">
-        <v>10.74</v>
+        <v>10.58</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -1423,51 +1423,51 @@
         </is>
       </c>
       <c r="J11" t="n">
-        <v>18910</v>
+        <v>80000</v>
       </c>
       <c r="K11" t="n">
-        <v>19050</v>
+        <v>82900</v>
       </c>
       <c r="L11" t="n">
-        <v>19050</v>
+        <v>83000</v>
       </c>
       <c r="M11" t="n">
-        <v>18090</v>
+        <v>75300</v>
       </c>
       <c r="N11" t="n">
-        <v>10.74</v>
+        <v>10.68</v>
       </c>
       <c r="O11" t="n">
-        <v>42205532415</v>
+        <v>73416899650</v>
       </c>
       <c r="P11" t="n">
-        <v>40350</v>
+        <v>184000</v>
       </c>
       <c r="Q11" t="n">
-        <v>3320</v>
+        <v>44750</v>
       </c>
       <c r="R11" t="n">
-        <v>-331000</v>
+        <v>-324000</v>
       </c>
       <c r="S11" t="n">
-        <v>-47000</v>
+        <v>-60000</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>공매도 장부 조작 및 대차 오링 의혹 제기. 대차해지 운동 참여 독려.</t>
+          <t>K-방산 관련 뉴스에 따른 기대감. 공매도 청산 및 주가 상승 전망.</t>
         </is>
       </c>
       <c r="U11" t="inlineStr"/>
       <c r="V11" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>['공매도', '대차', '주가 조작']</t>
+          <t>['K-방산', '공매도', '주가 상승']</t>
         </is>
       </c>
       <c r="X11" t="n">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
@@ -1476,90 +1476,90 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>047040</t>
+          <t>272210</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>가온전선</t>
+          <t>대한광통신</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>314500</v>
+        <v>17820</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>'-3.82%</t>
+          <t>'-2.73%</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>1.66</v>
+        <v>3.29</v>
       </c>
       <c r="E12" t="n">
-        <v>87</v>
+        <v>159</v>
       </c>
       <c r="F12" t="n">
-        <v>63</v>
+        <v>117</v>
       </c>
       <c r="G12" t="n">
-        <v>167</v>
+        <v>707</v>
       </c>
       <c r="H12" t="n">
-        <v>3.62</v>
+        <v>7.9</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J12" t="n">
-        <v>327000</v>
+        <v>18320</v>
       </c>
       <c r="K12" t="n">
-        <v>324000</v>
+        <v>18450</v>
       </c>
       <c r="L12" t="n">
-        <v>340500</v>
+        <v>18590</v>
       </c>
       <c r="M12" t="n">
-        <v>308500</v>
+        <v>17590</v>
       </c>
       <c r="N12" t="n">
-        <v>1.96</v>
+        <v>4.61</v>
       </c>
       <c r="O12" t="n">
-        <v>61767353250</v>
+        <v>149413859945</v>
       </c>
       <c r="P12" t="n">
-        <v>635000</v>
+        <v>31500</v>
       </c>
       <c r="Q12" t="n">
-        <v>52600</v>
+        <v>1272</v>
       </c>
       <c r="R12" t="n">
-        <v>-24000</v>
+        <v>-916000</v>
       </c>
       <c r="S12" t="n">
-        <v>-2000</v>
+        <v>0</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>일부 투자자들은 긍정적인 추세와 공급 계약을 언급하지만, 고평가 및 하락 의견도 존재하여 혼조세.</t>
+          <t>미국 광통신 AI주 급등에 따른 기대감 상승. 3만원 터치 및 연말, 내년 초까지 상승 전망.</t>
         </is>
       </c>
       <c r="U12" t="inlineStr"/>
       <c r="V12" t="n">
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>['공급 계약', '고평가', '추세']</t>
+          <t>['대한광통신', '광통신', 'AI']</t>
         </is>
       </c>
       <c r="X12" t="n">
-        <v>1</v>
+        <v>19</v>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
@@ -1568,97 +1568,373 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>000500</t>
+          <t>010170</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>오름테라퓨틱</t>
+          <t>대우건설</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>27100</v>
+        <v>18300</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>'-27.54%</t>
+          <t>'-3.23%</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="E13" t="n">
-        <v>472</v>
+        <v>47</v>
       </c>
       <c r="F13" t="n">
-        <v>268</v>
+        <v>35</v>
       </c>
       <c r="G13" t="n">
-        <v>906</v>
+        <v>201</v>
       </c>
       <c r="H13" t="n">
-        <v>7.09</v>
+        <v>10.74</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J13" t="n">
-        <v>37400</v>
+        <v>18910</v>
       </c>
       <c r="K13" t="n">
-        <v>26450</v>
+        <v>19050</v>
       </c>
       <c r="L13" t="n">
-        <v>28200</v>
+        <v>19050</v>
       </c>
       <c r="M13" t="n">
-        <v>26200</v>
+        <v>18090</v>
       </c>
       <c r="N13" t="n">
-        <v>7.08</v>
+        <v>10.74</v>
       </c>
       <c r="O13" t="n">
-        <v>60488955125</v>
+        <v>46534118780</v>
       </c>
       <c r="P13" t="n">
-        <v>146600</v>
+        <v>40350</v>
       </c>
       <c r="Q13" t="n">
-        <v>26200</v>
+        <v>3320</v>
       </c>
       <c r="R13" t="n">
-        <v>143000</v>
+        <v>-331000</v>
       </c>
       <c r="S13" t="n">
-        <v>42000</v>
+        <v>-47000</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>임상 진행 관련 불확실성 및 연속 하한가 발생. 투자자들의 신중한 접근 요구.</t>
+          <t>미국 종전 검토 및 공매도 관련 부정적 언급. 대차해지 운동 동참 호소.</t>
         </is>
       </c>
       <c r="U13" t="inlineStr"/>
       <c r="V13" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>['대우건설', '공매도', '대차해지']</t>
+        </is>
+      </c>
+      <c r="X13" t="n">
+        <v>20</v>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>활성</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>047040</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>대한전선</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>30300</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>'-3.66%</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="E14" t="n">
+        <v>58</v>
+      </c>
+      <c r="F14" t="n">
+        <v>37</v>
+      </c>
+      <c r="G14" t="n">
+        <v>108</v>
+      </c>
+      <c r="H14" t="n">
+        <v>11.92</v>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>MarketType.KOSPI</t>
+        </is>
+      </c>
+      <c r="J14" t="n">
+        <v>31450</v>
+      </c>
+      <c r="K14" t="n">
+        <v>31500</v>
+      </c>
+      <c r="L14" t="n">
+        <v>31550</v>
+      </c>
+      <c r="M14" t="n">
+        <v>29950</v>
+      </c>
+      <c r="N14" t="n">
+        <v>11.44</v>
+      </c>
+      <c r="O14" t="n">
+        <v>54951529975</v>
+      </c>
+      <c r="P14" t="n">
+        <v>75900</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>15000</v>
+      </c>
+      <c r="R14" t="n">
+        <v>-166000</v>
+      </c>
+      <c r="S14" t="n">
+        <v>-8000</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>반도체 장비 소부장 순환매 낙폭 과대 언급. 수급 불균형 및 주가 하락에 대한 부정적 시각.</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr"/>
+      <c r="V14" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>['대한전선', '반도체', '순환매']</t>
+        </is>
+      </c>
+      <c r="X14" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>활성</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>001440</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>가온전선</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>312000</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>'-4.59%</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="E15" t="n">
+        <v>92</v>
+      </c>
+      <c r="F15" t="n">
+        <v>68</v>
+      </c>
+      <c r="G15" t="n">
+        <v>179</v>
+      </c>
+      <c r="H15" t="n">
+        <v>3.62</v>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>MarketType.KOSPI</t>
+        </is>
+      </c>
+      <c r="J15" t="n">
+        <v>327000</v>
+      </c>
+      <c r="K15" t="n">
+        <v>324000</v>
+      </c>
+      <c r="L15" t="n">
+        <v>340500</v>
+      </c>
+      <c r="M15" t="n">
+        <v>308500</v>
+      </c>
+      <c r="N15" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="O15" t="n">
+        <v>64314748500</v>
+      </c>
+      <c r="P15" t="n">
+        <v>635000</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>52600</v>
+      </c>
+      <c r="R15" t="n">
+        <v>-24000</v>
+      </c>
+      <c r="S15" t="n">
+        <v>-2000</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>4381억 공급 계약 언급에도 불구하고 주가 하락세 보임. 일부 투자자는 과대평가 주장.</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr"/>
+      <c r="V15" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>['공급계약', '주가하락', '과대평가']</t>
+        </is>
+      </c>
+      <c r="X15" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>활성</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>000500</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>오름테라퓨틱</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>27650</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>'-26.07%</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E16" t="n">
+        <v>498</v>
+      </c>
+      <c r="F16" t="n">
+        <v>282</v>
+      </c>
+      <c r="G16" t="n">
+        <v>938</v>
+      </c>
+      <c r="H16" t="n">
+        <v>7.09</v>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>MarketType.KOSDAQ</t>
+        </is>
+      </c>
+      <c r="J16" t="n">
+        <v>37400</v>
+      </c>
+      <c r="K16" t="n">
+        <v>26450</v>
+      </c>
+      <c r="L16" t="n">
+        <v>28200</v>
+      </c>
+      <c r="M16" t="n">
+        <v>26200</v>
+      </c>
+      <c r="N16" t="n">
+        <v>7.08</v>
+      </c>
+      <c r="O16" t="n">
+        <v>62389426475</v>
+      </c>
+      <c r="P16" t="n">
+        <v>146600</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>26200</v>
+      </c>
+      <c r="R16" t="n">
+        <v>143000</v>
+      </c>
+      <c r="S16" t="n">
+        <v>42000</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>임상 진행 관련 불확실성 및 연속 하한가 발생. 투자자들의 신중한 접근 요구.</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr"/>
+      <c r="V16" t="n">
         <v>0.2</v>
       </c>
-      <c r="W13" t="inlineStr">
+      <c r="W16" t="inlineStr">
         <is>
           <t>['임상', '하한가', '바이오']</t>
         </is>
       </c>
-      <c r="X13" t="n">
+      <c r="X16" t="n">
         <v>1</v>
       </c>
-      <c r="Y13" t="inlineStr">
+      <c r="Y16" t="inlineStr">
         <is>
           <t>활성</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
+      <c r="Z16" t="inlineStr">
         <is>
           <t>475830</t>
         </is>

--- a/data/trending_integrated_20260921_10.xlsx
+++ b/data/trending_integrated_20260921_10.xlsx
@@ -567,24 +567,24 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>22800</v>
+        <v>22750</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>'+17.28%</t>
+          <t>'+17.03%</t>
         </is>
       </c>
       <c r="D2" t="n">
         <v>-0.04</v>
       </c>
       <c r="E2" t="n">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="F2" t="n">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="G2" t="n">
-        <v>142</v>
+        <v>155</v>
       </c>
       <c r="H2" t="n">
         <v>0.35</v>
@@ -610,7 +610,7 @@
         <v>0.39</v>
       </c>
       <c r="O2" t="n">
-        <v>133604175585</v>
+        <v>140394541110</v>
       </c>
       <c r="P2" t="n">
         <v>39350</v>
@@ -626,16 +626,16 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>美 타임 선정 '세계 최고 헬스테크 기업' 선정. 삼성과 4381억 계약 체결 및 5만원 이상 상승 전망.</t>
+          <t>美 타임 선정 '세계 최고 헬스테크 기업' 보도. 삼성과 대규모 공급 계약 체결 발표.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>['스카이랩스', '헬스테크', '타임']</t>
+          <t>['헬스테크', '타임', '공급계약']</t>
         </is>
       </c>
       <c r="X2" t="n">
@@ -655,31 +655,31 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>HLB</t>
+          <t>우리기술투자</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>33400</v>
+        <v>5990</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+12.65%</t>
+          <t>'+10.31%</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>-0.48</v>
+        <v>-0.31</v>
       </c>
       <c r="E3" t="n">
-        <v>144</v>
+        <v>43</v>
       </c>
       <c r="F3" t="n">
-        <v>109</v>
+        <v>24</v>
       </c>
       <c r="G3" t="n">
-        <v>783</v>
+        <v>118</v>
       </c>
       <c r="H3" t="n">
-        <v>16.67</v>
+        <v>0.19</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -687,47 +687,47 @@
         </is>
       </c>
       <c r="J3" t="n">
-        <v>29650</v>
+        <v>5430</v>
       </c>
       <c r="K3" t="n">
-        <v>30400</v>
+        <v>5710</v>
       </c>
       <c r="L3" t="n">
-        <v>33400</v>
+        <v>6280</v>
       </c>
       <c r="M3" t="n">
-        <v>29400</v>
+        <v>5600</v>
       </c>
       <c r="N3" t="n">
-        <v>17.15</v>
+        <v>0.5</v>
       </c>
       <c r="O3" t="n">
-        <v>14003134275</v>
+        <v>53342699680</v>
       </c>
       <c r="P3" t="n">
-        <v>69200</v>
+        <v>13140</v>
       </c>
       <c r="Q3" t="n">
-        <v>24150</v>
+        <v>3725</v>
       </c>
       <c r="R3" t="n">
-        <v>-37000</v>
+        <v>-148000</v>
       </c>
       <c r="S3" t="n">
-        <v>-1000</v>
+        <v>0</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>FDA 승인 관련 기대와 불확실성 혼재. 임상 성공 여부 및 주가 패턴에 대한 논쟁.</t>
+          <t>비트코인 상승에 따른 기대감. 신한투자증권의 공매도 행위에 대한 비판.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
-        <v>0.2</v>
+        <v>0.5</v>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>['FDA승인', '임상성공', '주가패턴']</t>
+          <t>['비트코인', '우리기술투자', '공매도']</t>
         </is>
       </c>
       <c r="X3" t="n">
@@ -740,38 +740,38 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>028300</t>
+          <t>041190</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>우리기술투자</t>
+          <t>HLB</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>6040</v>
+        <v>31400</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+11.23%</t>
+          <t>'+5.90%</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>-0.31</v>
+        <v>-0.48</v>
       </c>
       <c r="E4" t="n">
-        <v>41</v>
+        <v>189</v>
       </c>
       <c r="F4" t="n">
-        <v>24</v>
+        <v>133</v>
       </c>
       <c r="G4" t="n">
-        <v>110</v>
+        <v>889</v>
       </c>
       <c r="H4" t="n">
-        <v>0.19</v>
+        <v>16.67</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -779,47 +779,47 @@
         </is>
       </c>
       <c r="J4" t="n">
-        <v>5430</v>
+        <v>29650</v>
       </c>
       <c r="K4" t="n">
-        <v>5710</v>
+        <v>30400</v>
       </c>
       <c r="L4" t="n">
-        <v>6280</v>
+        <v>33400</v>
       </c>
       <c r="M4" t="n">
-        <v>5600</v>
+        <v>29400</v>
       </c>
       <c r="N4" t="n">
-        <v>0.5</v>
+        <v>17.15</v>
       </c>
       <c r="O4" t="n">
-        <v>52605612475</v>
+        <v>19410173850</v>
       </c>
       <c r="P4" t="n">
-        <v>13140</v>
+        <v>69200</v>
       </c>
       <c r="Q4" t="n">
-        <v>3725</v>
+        <v>24150</v>
       </c>
       <c r="R4" t="n">
-        <v>-148000</v>
+        <v>-37000</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>-1000</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>비트코인 81,500달러 돌파에 따른 기대감 상승. 공매도 세력에 대한 부정적 언급 및 매수세 유입.</t>
+          <t>FDA 승인 관련 기대와 불확실성 혼재. 임상 성공 여부 및 주가 패턴에 대한 논쟁.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['우리기술투자', '비트코인', '공매도']</t>
+          <t>['FDA승인', '임상성공', '주가패턴']</t>
         </is>
       </c>
       <c r="X4" t="n">
@@ -832,38 +832,38 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>041190</t>
+          <t>028300</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>삼성전자우</t>
+          <t>광전자</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>207000</v>
+        <v>11120</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+5.56%</t>
+          <t>'+5.70%</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>-0.09</v>
+        <v>0.16</v>
       </c>
       <c r="E5" t="n">
-        <v>40</v>
+        <v>66</v>
       </c>
       <c r="F5" t="n">
-        <v>34</v>
+        <v>47</v>
       </c>
       <c r="G5" t="n">
-        <v>175</v>
+        <v>124</v>
       </c>
       <c r="H5" t="n">
-        <v>75.44</v>
+        <v>18.29</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -871,51 +871,51 @@
         </is>
       </c>
       <c r="J5" t="n">
-        <v>196100</v>
+        <v>10520</v>
       </c>
       <c r="K5" t="n">
-        <v>199800</v>
+        <v>10780</v>
       </c>
       <c r="L5" t="n">
-        <v>207000</v>
+        <v>12190</v>
       </c>
       <c r="M5" t="n">
-        <v>199600</v>
+        <v>10590</v>
       </c>
       <c r="N5" t="n">
-        <v>75.53</v>
+        <v>18.13</v>
       </c>
       <c r="O5" t="n">
-        <v>394884304300</v>
+        <v>157369962245</v>
       </c>
       <c r="P5" t="n">
-        <v>243500</v>
+        <v>22450</v>
       </c>
       <c r="Q5" t="n">
-        <v>64700</v>
+        <v>1760</v>
       </c>
       <c r="R5" t="n">
-        <v>398000</v>
+        <v>-18000</v>
       </c>
       <c r="S5" t="n">
-        <v>-36000</v>
+        <v>0</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>배당락 D-4일, 우선주 자사주 취득소각 기대감. 20만원 돌파 및 20만 7천원, 21만원 목표.</t>
+          <t>미국 시장 광통신주 급등에 따른 기대감. 그러나 추격 매수 시 주의 필요.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>0.5</v>
+        <v>0.2</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['삼성전자우', '배당', '자사주']</t>
+          <t>['광통신', '추격매수']</t>
         </is>
       </c>
       <c r="X5" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
@@ -924,38 +924,38 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>005935</t>
+          <t>017900</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>광전자</t>
+          <t>삼성전자우</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>11070</v>
+        <v>207000</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'+5.23%</t>
+          <t>'+5.56%</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>0.16</v>
+        <v>-0.09</v>
       </c>
       <c r="E6" t="n">
-        <v>70</v>
+        <v>45</v>
       </c>
       <c r="F6" t="n">
-        <v>51</v>
+        <v>37</v>
       </c>
       <c r="G6" t="n">
-        <v>127</v>
+        <v>182</v>
       </c>
       <c r="H6" t="n">
-        <v>18.29</v>
+        <v>75.44</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -963,51 +963,51 @@
         </is>
       </c>
       <c r="J6" t="n">
-        <v>10520</v>
+        <v>196100</v>
       </c>
       <c r="K6" t="n">
-        <v>10780</v>
+        <v>199800</v>
       </c>
       <c r="L6" t="n">
-        <v>12190</v>
+        <v>207500</v>
       </c>
       <c r="M6" t="n">
-        <v>10590</v>
+        <v>199600</v>
       </c>
       <c r="N6" t="n">
-        <v>18.13</v>
+        <v>75.53</v>
       </c>
       <c r="O6" t="n">
-        <v>154117913460</v>
+        <v>422826184300</v>
       </c>
       <c r="P6" t="n">
-        <v>22450</v>
+        <v>243500</v>
       </c>
       <c r="Q6" t="n">
-        <v>1760</v>
+        <v>64700</v>
       </c>
       <c r="R6" t="n">
-        <v>-18000</v>
+        <v>398000</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>-36000</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>미국 광통신주 급등에 따른 기대감 상승. 하지만 추격 매수 및 투자 주의 언급.</t>
+          <t>삼성전자 우선주, 배당락 기대감 및 자사주 취득/소각 뉴스 언급. 본주 대비 저평가 주장.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['광통신', '나스닥선물', '추격매수']</t>
+          <t>['우선주', '배당락', '자사주']</t>
         </is>
       </c>
       <c r="X6" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
@@ -1016,7 +1016,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>017900</t>
+          <t>005935</t>
         </is>
       </c>
     </row>
@@ -1027,24 +1027,24 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>271500</v>
+        <v>271250</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'+4.02%</t>
+          <t>'+3.93%</t>
         </is>
       </c>
       <c r="D7" t="n">
         <v>-0.02</v>
       </c>
       <c r="E7" t="n">
-        <v>658</v>
+        <v>684</v>
       </c>
       <c r="F7" t="n">
-        <v>426</v>
+        <v>439</v>
       </c>
       <c r="G7" t="n">
-        <v>2655</v>
+        <v>2797</v>
       </c>
       <c r="H7" t="n">
         <v>46.46</v>
@@ -1070,7 +1070,7 @@
         <v>46.48</v>
       </c>
       <c r="O7" t="n">
-        <v>2117467782250</v>
+        <v>2244845054250</v>
       </c>
       <c r="P7" t="n">
         <v>374500</v>
@@ -1130,13 +1130,13 @@
         <v>0.13</v>
       </c>
       <c r="E8" t="n">
-        <v>711</v>
+        <v>728</v>
       </c>
       <c r="F8" t="n">
-        <v>429</v>
+        <v>435</v>
       </c>
       <c r="G8" t="n">
-        <v>2761</v>
+        <v>2807</v>
       </c>
       <c r="H8" t="n">
         <v>50.23</v>
@@ -1162,7 +1162,7 @@
         <v>50.1</v>
       </c>
       <c r="O8" t="n">
-        <v>1722613367500</v>
+        <v>1863385637000</v>
       </c>
       <c r="P8" t="n">
         <v>2987000</v>
@@ -1211,24 +1211,24 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>13870</v>
+        <v>13820</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>'+0.00%</t>
+          <t>'-0.36%</t>
         </is>
       </c>
       <c r="D9" t="n">
         <v>0.58</v>
       </c>
       <c r="E9" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F9" t="n">
         <v>24</v>
       </c>
       <c r="G9" t="n">
-        <v>212</v>
+        <v>223</v>
       </c>
       <c r="H9" t="n">
         <v>5.5</v>
@@ -1254,7 +1254,7 @@
         <v>4.92</v>
       </c>
       <c r="O9" t="n">
-        <v>49925552850</v>
+        <v>50942320575</v>
       </c>
       <c r="P9" t="n">
         <v>30200</v>
@@ -1270,16 +1270,16 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>미 증권가 원전 관련 긍정적 전망. 신용 증가 및 프로그램 매매 동향 언급.</t>
+          <t>원전 관련 기대감 언급. 신한투자증권의 공매도 의혹 및 주가 하락에 대한 불만.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['우리기술', '원전', '프로그램']</t>
+          <t>['원전', '신한투자증권', '공매도']</t>
         </is>
       </c>
       <c r="X9" t="n">
@@ -1303,24 +1303,24 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>4185</v>
+        <v>4175</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'-0.83%</t>
+          <t>'-1.07%</t>
         </is>
       </c>
       <c r="D10" t="n">
         <v>-0.22</v>
       </c>
       <c r="E10" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F10" t="n">
         <v>37</v>
       </c>
       <c r="G10" t="n">
-        <v>135</v>
+        <v>154</v>
       </c>
       <c r="H10" t="n">
         <v>0.33</v>
@@ -1346,7 +1346,7 @@
         <v>0.55</v>
       </c>
       <c r="O10" t="n">
-        <v>24572543174</v>
+        <v>24888040552</v>
       </c>
       <c r="P10" t="n">
         <v>6480</v>
@@ -1362,16 +1362,16 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>코인 관련주 및 미버스 급등 속 상대적 부진. 거래량 부족 및 매도 폭탄 언급.</t>
+          <t>코인 관련주 및 미버스 급등 속 상대적 부진. 거래량 부족 및 재료 소멸 우려.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>['미투온', '코인', '미버스']</t>
+          <t>['코인관련주', '미버스', '거래량']</t>
         </is>
       </c>
       <c r="X10" t="n">
@@ -1406,13 +1406,13 @@
         <v>-0.1</v>
       </c>
       <c r="E11" t="n">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="F11" t="n">
         <v>69</v>
       </c>
       <c r="G11" t="n">
-        <v>471</v>
+        <v>522</v>
       </c>
       <c r="H11" t="n">
         <v>10.58</v>
@@ -1438,7 +1438,7 @@
         <v>10.68</v>
       </c>
       <c r="O11" t="n">
-        <v>73416899650</v>
+        <v>76416388500</v>
       </c>
       <c r="P11" t="n">
         <v>184000</v>
@@ -1454,16 +1454,16 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>K-방산 관련 뉴스에 따른 기대감. 공매도 청산 및 주가 상승 전망.</t>
+          <t>K-방산 관련 뉴스에 따른 기대감. 공매도 세력에 대한 불만 및 주가 상승 전망.</t>
         </is>
       </c>
       <c r="U11" t="inlineStr"/>
       <c r="V11" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>['K-방산', '공매도', '주가 상승']</t>
+          <t>['K-방산', '드론', '공매도']</t>
         </is>
       </c>
       <c r="X11" t="n">
@@ -1487,11 +1487,11 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>17820</v>
+        <v>17730</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>'-2.73%</t>
+          <t>'-3.22%</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -1501,10 +1501,10 @@
         <v>159</v>
       </c>
       <c r="F12" t="n">
-        <v>117</v>
+        <v>112</v>
       </c>
       <c r="G12" t="n">
-        <v>707</v>
+        <v>690</v>
       </c>
       <c r="H12" t="n">
         <v>7.9</v>
@@ -1530,7 +1530,7 @@
         <v>4.61</v>
       </c>
       <c r="O12" t="n">
-        <v>149413859945</v>
+        <v>154024438620</v>
       </c>
       <c r="P12" t="n">
         <v>31500</v>
@@ -1546,16 +1546,16 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>미국 광통신 AI주 급등에 따른 기대감 상승. 3만원 터치 및 연말, 내년 초까지 상승 전망.</t>
+          <t>미국 시장 광통신주 급등 및 AI주 동반 상승. 기관 매수에 따른 긍정적 전망.</t>
         </is>
       </c>
       <c r="U12" t="inlineStr"/>
       <c r="V12" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>['대한광통신', '광통신', 'AI']</t>
+          <t>['광통신', 'AI주', '기관매수']</t>
         </is>
       </c>
       <c r="X12" t="n">
@@ -1579,24 +1579,24 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>18300</v>
+        <v>18280</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>'-3.23%</t>
+          <t>'-3.33%</t>
         </is>
       </c>
       <c r="D13" t="n">
         <v>0</v>
       </c>
       <c r="E13" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F13" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G13" t="n">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="H13" t="n">
         <v>10.74</v>
@@ -1622,7 +1622,7 @@
         <v>10.74</v>
       </c>
       <c r="O13" t="n">
-        <v>46534118780</v>
+        <v>48316449760</v>
       </c>
       <c r="P13" t="n">
         <v>40350</v>
@@ -1638,7 +1638,7 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>미국 종전 검토 및 공매도 관련 부정적 언급. 대차해지 운동 동참 호소.</t>
+          <t>공매도 관련 논란 및 대차해지 운동 동참 요구. 주가 하락 추세에 대한 불만.</t>
         </is>
       </c>
       <c r="U13" t="inlineStr"/>
@@ -1647,7 +1647,7 @@
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>['대우건설', '공매도', '대차해지']</t>
+          <t>['공매도', '대차해지']</t>
         </is>
       </c>
       <c r="X13" t="n">
@@ -1671,24 +1671,24 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>30300</v>
+        <v>30350</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>'-3.66%</t>
+          <t>'-3.50%</t>
         </is>
       </c>
       <c r="D14" t="n">
         <v>0.48</v>
       </c>
       <c r="E14" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="F14" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G14" t="n">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="H14" t="n">
         <v>11.92</v>
@@ -1714,7 +1714,7 @@
         <v>11.44</v>
       </c>
       <c r="O14" t="n">
-        <v>54951529975</v>
+        <v>56285610850</v>
       </c>
       <c r="P14" t="n">
         <v>75900</v>
@@ -1730,7 +1730,7 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>반도체 장비 소부장 순환매 낙폭 과대 언급. 수급 불균형 및 주가 하락에 대한 부정적 시각.</t>
+          <t>개인 투자자의 대한전선 매도 및 전선주 하락세 언급. 수급 불균형 우려.</t>
         </is>
       </c>
       <c r="U14" t="inlineStr"/>
@@ -1739,7 +1739,7 @@
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>['대한전선', '반도체', '순환매']</t>
+          <t>['전선주', '매도', '수급']</t>
         </is>
       </c>
       <c r="X14" t="n">
@@ -1763,24 +1763,24 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>312000</v>
+        <v>311000</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>'-4.59%</t>
+          <t>'-4.89%</t>
         </is>
       </c>
       <c r="D15" t="n">
         <v>1.66</v>
       </c>
       <c r="E15" t="n">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="F15" t="n">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="G15" t="n">
-        <v>179</v>
+        <v>186</v>
       </c>
       <c r="H15" t="n">
         <v>3.62</v>
@@ -1806,7 +1806,7 @@
         <v>1.96</v>
       </c>
       <c r="O15" t="n">
-        <v>64314748500</v>
+        <v>65868693500</v>
       </c>
       <c r="P15" t="n">
         <v>635000</v>
@@ -1822,16 +1822,16 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>4381억 공급 계약 언급에도 불구하고 주가 하락세 보임. 일부 투자자는 과대평가 주장.</t>
+          <t>4381억 공급 계약 언급. 긍정적 조정 구간으로 해석. 신한증권에 대한 부정적 언급.</t>
         </is>
       </c>
       <c r="U15" t="inlineStr"/>
       <c r="V15" t="n">
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>['공급계약', '주가하락', '과대평가']</t>
+          <t>['공급계약', '조정구간', '신한증권']</t>
         </is>
       </c>
       <c r="X15" t="n">
@@ -1855,24 +1855,24 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>27650</v>
+        <v>27750</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>'-26.07%</t>
+          <t>'-25.80%</t>
         </is>
       </c>
       <c r="D16" t="n">
         <v>0.01</v>
       </c>
       <c r="E16" t="n">
-        <v>498</v>
+        <v>510</v>
       </c>
       <c r="F16" t="n">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="G16" t="n">
-        <v>938</v>
+        <v>936</v>
       </c>
       <c r="H16" t="n">
         <v>7.09</v>
@@ -1898,7 +1898,7 @@
         <v>7.08</v>
       </c>
       <c r="O16" t="n">
-        <v>62389426475</v>
+        <v>65600722100</v>
       </c>
       <c r="P16" t="n">
         <v>146600</v>

--- a/data/trending_integrated_20260921_10.xlsx
+++ b/data/trending_integrated_20260921_10.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z16"/>
+  <dimension ref="A1:Z18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -567,24 +567,24 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>22750</v>
+        <v>24050</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>'+17.03%</t>
+          <t>'+23.71%</t>
         </is>
       </c>
       <c r="D2" t="n">
         <v>-0.04</v>
       </c>
       <c r="E2" t="n">
-        <v>83</v>
+        <v>96</v>
       </c>
       <c r="F2" t="n">
-        <v>68</v>
+        <v>75</v>
       </c>
       <c r="G2" t="n">
-        <v>155</v>
+        <v>167</v>
       </c>
       <c r="H2" t="n">
         <v>0.35</v>
@@ -601,7 +601,7 @@
         <v>20200</v>
       </c>
       <c r="L2" t="n">
-        <v>24050</v>
+        <v>24150</v>
       </c>
       <c r="M2" t="n">
         <v>19610</v>
@@ -610,7 +610,7 @@
         <v>0.39</v>
       </c>
       <c r="O2" t="n">
-        <v>140394541110</v>
+        <v>160650885860</v>
       </c>
       <c r="P2" t="n">
         <v>39350</v>
@@ -626,16 +626,16 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>美 타임 선정 '세계 최고 헬스테크 기업' 보도. 삼성과 대규모 공급 계약 체결 발표.</t>
+          <t>스카이랩스, 美 타임 선정 '세계 최고 헬스테크 기업' 그룹 선정 소식에 주가 급등. 2주간의 하락 후 반등하며 세계적 인정에 대한 기대감 고조. 기관 및 외국인 프로그램 매수세 유입, 9%대 상승 기록.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>['헬스테크', '타임', '공급계약']</t>
+          <t>['헬스테크', '타임지', '기관외국인']</t>
         </is>
       </c>
       <c r="X2" t="n">
@@ -655,31 +655,31 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>우리기술투자</t>
+          <t>SFA반도체</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>5990</v>
+        <v>10740</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+10.31%</t>
+          <t>'+19.07%</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>-0.31</v>
+        <v>0.09</v>
       </c>
       <c r="E3" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F3" t="n">
-        <v>24</v>
+        <v>37</v>
       </c>
       <c r="G3" t="n">
-        <v>118</v>
+        <v>95</v>
       </c>
       <c r="H3" t="n">
-        <v>0.19</v>
+        <v>8.6</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -687,47 +687,47 @@
         </is>
       </c>
       <c r="J3" t="n">
-        <v>5430</v>
+        <v>9020</v>
       </c>
       <c r="K3" t="n">
-        <v>5710</v>
+        <v>9050</v>
       </c>
       <c r="L3" t="n">
-        <v>6280</v>
+        <v>10910</v>
       </c>
       <c r="M3" t="n">
-        <v>5600</v>
+        <v>9010</v>
       </c>
       <c r="N3" t="n">
-        <v>0.5</v>
+        <v>8.51</v>
       </c>
       <c r="O3" t="n">
-        <v>53342699680</v>
+        <v>149619179155</v>
       </c>
       <c r="P3" t="n">
-        <v>13140</v>
+        <v>11640</v>
       </c>
       <c r="Q3" t="n">
-        <v>3725</v>
+        <v>3735</v>
       </c>
       <c r="R3" t="n">
-        <v>-148000</v>
+        <v>165000</v>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>비트코인 상승에 따른 기대감. 신한투자증권의 공매도 행위에 대한 비판.</t>
+          <t>SFA반도체, 삼성전자와의 대규모 공급 계약 체결 소식에 급등. 후공정 대장주로서의 입지 강화 및 4000원 돌파 후 전고점 돌파 기대감 고조. 15000원 목표가 제시 및 상승 추세 지속 가능성 언급.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>['비트코인', '우리기술투자', '공매도']</t>
+          <t>['공급계약', '후공정', '추세']</t>
         </is>
       </c>
       <c r="X3" t="n">
@@ -740,38 +740,38 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>041190</t>
+          <t>036540</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>HLB</t>
+          <t>우리기술투자</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>31400</v>
+        <v>5925</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+5.90%</t>
+          <t>'+9.12%</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>-0.48</v>
+        <v>-0.31</v>
       </c>
       <c r="E4" t="n">
-        <v>189</v>
+        <v>44</v>
       </c>
       <c r="F4" t="n">
-        <v>133</v>
+        <v>24</v>
       </c>
       <c r="G4" t="n">
-        <v>889</v>
+        <v>118</v>
       </c>
       <c r="H4" t="n">
-        <v>16.67</v>
+        <v>0.19</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -779,47 +779,47 @@
         </is>
       </c>
       <c r="J4" t="n">
-        <v>29650</v>
+        <v>5430</v>
       </c>
       <c r="K4" t="n">
-        <v>30400</v>
+        <v>5710</v>
       </c>
       <c r="L4" t="n">
-        <v>33400</v>
+        <v>6280</v>
       </c>
       <c r="M4" t="n">
-        <v>29400</v>
+        <v>5600</v>
       </c>
       <c r="N4" t="n">
-        <v>17.15</v>
+        <v>0.5</v>
       </c>
       <c r="O4" t="n">
-        <v>19410173850</v>
+        <v>54016565995</v>
       </c>
       <c r="P4" t="n">
-        <v>69200</v>
+        <v>13140</v>
       </c>
       <c r="Q4" t="n">
-        <v>24150</v>
+        <v>3725</v>
       </c>
       <c r="R4" t="n">
-        <v>-37000</v>
+        <v>-148000</v>
       </c>
       <c r="S4" t="n">
-        <v>-1000</v>
+        <v>0</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>FDA 승인 관련 기대와 불확실성 혼재. 임상 성공 여부 및 주가 패턴에 대한 논쟁.</t>
+          <t>비트코인 가격 상승 반전에 따라 우리기술투자 주가 급등. 신한투자증권 공매도 의혹 제기 및 민원 제기 움직임. 7천 원 목표가 제시하며 비트코인 흐름에 따른 주가 상승 기대감 형성.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['FDA승인', '임상성공', '주가패턴']</t>
+          <t>['비트코인', '공매도', '신한투자증권']</t>
         </is>
       </c>
       <c r="X4" t="n">
@@ -832,77 +832,77 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>028300</t>
+          <t>041190</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>광전자</t>
+          <t>HLB</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>11120</v>
+        <v>31500</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+5.70%</t>
+          <t>'+6.24%</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>0.16</v>
+        <v>-0.48</v>
       </c>
       <c r="E5" t="n">
-        <v>66</v>
+        <v>236</v>
       </c>
       <c r="F5" t="n">
-        <v>47</v>
+        <v>165</v>
       </c>
       <c r="G5" t="n">
-        <v>124</v>
+        <v>962</v>
       </c>
       <c r="H5" t="n">
-        <v>18.29</v>
+        <v>16.67</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J5" t="n">
-        <v>10520</v>
+        <v>29650</v>
       </c>
       <c r="K5" t="n">
-        <v>10780</v>
+        <v>30400</v>
       </c>
       <c r="L5" t="n">
-        <v>12190</v>
+        <v>33400</v>
       </c>
       <c r="M5" t="n">
-        <v>10590</v>
+        <v>29400</v>
       </c>
       <c r="N5" t="n">
-        <v>18.13</v>
+        <v>17.15</v>
       </c>
       <c r="O5" t="n">
-        <v>157369962245</v>
+        <v>20664938425</v>
       </c>
       <c r="P5" t="n">
-        <v>22450</v>
+        <v>69200</v>
       </c>
       <c r="Q5" t="n">
-        <v>1760</v>
+        <v>24150</v>
       </c>
       <c r="R5" t="n">
-        <v>-18000</v>
+        <v>-37000</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>-1000</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>미국 시장 광통신주 급등에 따른 기대감. 그러나 추격 매수 시 주의 필요.</t>
+          <t>FDA 승인 관련 기대와 불확실성 혼재. 임상 성공 여부 및 주가 패턴에 대한 논쟁.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
@@ -911,11 +911,11 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['광통신', '추격매수']</t>
+          <t>['FDA승인', '임상성공', '주가패턴']</t>
         </is>
       </c>
       <c r="X5" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
@@ -924,7 +924,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>017900</t>
+          <t>028300</t>
         </is>
       </c>
     </row>
@@ -935,24 +935,24 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>207000</v>
+        <v>207500</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'+5.56%</t>
+          <t>'+5.81%</t>
         </is>
       </c>
       <c r="D6" t="n">
         <v>-0.09</v>
       </c>
       <c r="E6" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F6" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G6" t="n">
-        <v>182</v>
+        <v>199</v>
       </c>
       <c r="H6" t="n">
         <v>75.44</v>
@@ -978,7 +978,7 @@
         <v>75.53</v>
       </c>
       <c r="O6" t="n">
-        <v>422826184300</v>
+        <v>431361341300</v>
       </c>
       <c r="P6" t="n">
         <v>243500</v>
@@ -994,7 +994,7 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>삼성전자 우선주, 배당락 기대감 및 자사주 취득/소각 뉴스 언급. 본주 대비 저평가 주장.</t>
+          <t>삼성전자 우선주, 배당 기대감과 자사주 취득 소각 뉴스에 힘입어 강세 전망. 본주 매입 완료 후 물량 풀릴 가능성 및 배당락 영향에 대한 상반된 의견 존재. 20만 원대 매수 후 장기 보유 전략 제시.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
@@ -1003,7 +1003,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['우선주', '배당락', '자사주']</t>
+          <t>['배당', '자사주', '전망']</t>
         </is>
       </c>
       <c r="X6" t="n">
@@ -1023,31 +1023,31 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>광전자</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>271250</v>
+        <v>11090</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'+3.93%</t>
+          <t>'+5.42%</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>-0.02</v>
+        <v>0.16</v>
       </c>
       <c r="E7" t="n">
-        <v>684</v>
+        <v>70</v>
       </c>
       <c r="F7" t="n">
-        <v>439</v>
+        <v>49</v>
       </c>
       <c r="G7" t="n">
-        <v>2797</v>
+        <v>135</v>
       </c>
       <c r="H7" t="n">
-        <v>46.46</v>
+        <v>18.29</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -1055,51 +1055,51 @@
         </is>
       </c>
       <c r="J7" t="n">
-        <v>261000</v>
+        <v>10520</v>
       </c>
       <c r="K7" t="n">
-        <v>264000</v>
+        <v>10780</v>
       </c>
       <c r="L7" t="n">
-        <v>272000</v>
+        <v>12190</v>
       </c>
       <c r="M7" t="n">
-        <v>263500</v>
+        <v>10590</v>
       </c>
       <c r="N7" t="n">
-        <v>46.48</v>
+        <v>18.13</v>
       </c>
       <c r="O7" t="n">
-        <v>2244845054250</v>
+        <v>158705410680</v>
       </c>
       <c r="P7" t="n">
-        <v>374500</v>
+        <v>22450</v>
       </c>
       <c r="Q7" t="n">
-        <v>81100</v>
+        <v>1760</v>
       </c>
       <c r="R7" t="n">
-        <v>2588000</v>
+        <v>-18000</v>
       </c>
       <c r="S7" t="n">
-        <v>189000</v>
+        <v>0</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>AI 감속론 부인 및 배당 기대감으로 인한 상승 전망. 신한증권 시스템 오류에 대한 불만 제기.</t>
+          <t>미국 광통신주 급등에 영향을 받으며 국내 증시도 동반 상승 기대. 그러나 개인 투자자들의 매도 심리 및 차익 실현 매물 출현 가능성으로 단기적인 조정 우려. 높은 변동성 속 신중한 접근 필요.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['AI', '배당', '상승장']</t>
+          <t>['광통신', '추세', '변동성']</t>
         </is>
       </c>
       <c r="X7" t="n">
-        <v>110</v>
+        <v>6</v>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
@@ -1108,38 +1108,38 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>005930</t>
+          <t>017900</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1877000</v>
+        <v>271500</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'+1.08%</t>
+          <t>'+4.02%</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>0.13</v>
+        <v>-0.02</v>
       </c>
       <c r="E8" t="n">
-        <v>728</v>
+        <v>717</v>
       </c>
       <c r="F8" t="n">
-        <v>435</v>
+        <v>453</v>
       </c>
       <c r="G8" t="n">
-        <v>2807</v>
+        <v>2945</v>
       </c>
       <c r="H8" t="n">
-        <v>50.23</v>
+        <v>46.46</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -1147,51 +1147,51 @@
         </is>
       </c>
       <c r="J8" t="n">
-        <v>1857000</v>
+        <v>261000</v>
       </c>
       <c r="K8" t="n">
-        <v>1872000</v>
+        <v>264000</v>
       </c>
       <c r="L8" t="n">
-        <v>1888000</v>
+        <v>272000</v>
       </c>
       <c r="M8" t="n">
-        <v>1847000</v>
+        <v>263500</v>
       </c>
       <c r="N8" t="n">
-        <v>50.1</v>
+        <v>46.48</v>
       </c>
       <c r="O8" t="n">
-        <v>1863385637000</v>
+        <v>2318122482000</v>
       </c>
       <c r="P8" t="n">
-        <v>2987000</v>
+        <v>374500</v>
       </c>
       <c r="Q8" t="n">
-        <v>333000</v>
+        <v>81100</v>
       </c>
       <c r="R8" t="n">
-        <v>-78000</v>
+        <v>2588000</v>
       </c>
       <c r="S8" t="n">
-        <v>55000</v>
+        <v>189000</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>미국 증시 반도체주 급등 및 HBM 시장 성장 전망. 20만원 돌파 및 분기 사상 최고 영업이익 예상.</t>
+          <t>내년 상반기까지 상승장 기대감 속 삼성전자 주가 상승 전망. AI 감속론은 부정적 전망으로 작용할 수 있으나, 배당 효과 및 경쟁사 주가 상승이 긍정적 요인으로 작용. 증권사 시스템 장애 이슈는 단기적 투자 심리에 영향.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="n">
-        <v>0.6</v>
+        <v>0.3</v>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>['SK하이닉스', 'HBM', '반도체']</t>
+          <t>['AI', '배당', '전망']</t>
         </is>
       </c>
       <c r="X8" t="n">
-        <v>75</v>
+        <v>110</v>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
@@ -1200,90 +1200,90 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>000660</t>
+          <t>005930</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>우리기술</t>
+          <t>SK하이닉스</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>13820</v>
+        <v>1878000</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>'-0.36%</t>
+          <t>'+1.13%</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>0.58</v>
+        <v>0.13</v>
       </c>
       <c r="E9" t="n">
-        <v>40</v>
+        <v>748</v>
       </c>
       <c r="F9" t="n">
-        <v>24</v>
+        <v>444</v>
       </c>
       <c r="G9" t="n">
-        <v>223</v>
+        <v>2872</v>
       </c>
       <c r="H9" t="n">
-        <v>5.5</v>
+        <v>50.23</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J9" t="n">
-        <v>13870</v>
+        <v>1857000</v>
       </c>
       <c r="K9" t="n">
-        <v>14070</v>
+        <v>1872000</v>
       </c>
       <c r="L9" t="n">
-        <v>14790</v>
+        <v>1888000</v>
       </c>
       <c r="M9" t="n">
-        <v>13760</v>
+        <v>1847000</v>
       </c>
       <c r="N9" t="n">
-        <v>4.92</v>
+        <v>50.1</v>
       </c>
       <c r="O9" t="n">
-        <v>50942320575</v>
+        <v>1969961380000</v>
       </c>
       <c r="P9" t="n">
-        <v>30200</v>
+        <v>2987000</v>
       </c>
       <c r="Q9" t="n">
-        <v>3540</v>
+        <v>333000</v>
       </c>
       <c r="R9" t="n">
-        <v>-179000</v>
+        <v>-78000</v>
       </c>
       <c r="S9" t="n">
-        <v>-3000</v>
+        <v>55000</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>원전 관련 기대감 언급. 신한투자증권의 공매도 의혹 및 주가 하락에 대한 불만.</t>
+          <t>미국 증시 반도체주 급등 및 HBM 시장 성장 전망. 20만원 돌파 및 분기 사상 최고 영업이익 예상.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="n">
-        <v>0.1</v>
+        <v>0.6</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['원전', '신한투자증권', '공매도']</t>
+          <t>['SK하이닉스', 'HBM', '반도체']</t>
         </is>
       </c>
       <c r="X9" t="n">
-        <v>3</v>
+        <v>75</v>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
@@ -1292,38 +1292,38 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>032820</t>
+          <t>000660</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>미투온</t>
+          <t>성호전자</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>4175</v>
+        <v>26900</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'-1.07%</t>
+          <t>'+0.37%</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>-0.22</v>
+        <v>-0.3</v>
       </c>
       <c r="E10" t="n">
-        <v>61</v>
+        <v>40</v>
       </c>
       <c r="F10" t="n">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="G10" t="n">
-        <v>154</v>
+        <v>93</v>
       </c>
       <c r="H10" t="n">
-        <v>0.33</v>
+        <v>2.11</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -1331,51 +1331,51 @@
         </is>
       </c>
       <c r="J10" t="n">
-        <v>4220</v>
+        <v>26800</v>
       </c>
       <c r="K10" t="n">
-        <v>4220</v>
+        <v>27400</v>
       </c>
       <c r="L10" t="n">
-        <v>4415</v>
+        <v>27750</v>
       </c>
       <c r="M10" t="n">
-        <v>4125</v>
+        <v>25650</v>
       </c>
       <c r="N10" t="n">
-        <v>0.55</v>
+        <v>2.41</v>
       </c>
       <c r="O10" t="n">
-        <v>24888040552</v>
+        <v>95160757725</v>
       </c>
       <c r="P10" t="n">
-        <v>6480</v>
+        <v>59600</v>
       </c>
       <c r="Q10" t="n">
-        <v>1738</v>
+        <v>1030</v>
       </c>
       <c r="R10" t="n">
-        <v>121000</v>
+        <v>-266000</v>
       </c>
       <c r="S10" t="n">
         <v>0</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>코인 관련주 및 미버스 급등 속 상대적 부진. 거래량 부족 및 재료 소멸 우려.</t>
+          <t>성호전자, 3일간의 폭등 후 차익 실현 매물 출현 가능성 언급. 외인·기관 쌍끌이 매수세 유입 및 10만 원 이상 상승 가능성 제시. 자회사 상장 반대 등 잠재적 리스크 요인 존재.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>['코인관련주', '미버스', '거래량']</t>
+          <t>['폭등', '외인기관', '상승가능성']</t>
         </is>
       </c>
       <c r="X10" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
@@ -1384,90 +1384,90 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>201490</t>
+          <t>043260</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>한화시스템</t>
+          <t>우리기술</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>79000</v>
+        <v>13800</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>'-1.25%</t>
+          <t>'-0.50%</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>-0.1</v>
+        <v>0.58</v>
       </c>
       <c r="E11" t="n">
-        <v>119</v>
+        <v>42</v>
       </c>
       <c r="F11" t="n">
-        <v>69</v>
+        <v>26</v>
       </c>
       <c r="G11" t="n">
-        <v>522</v>
+        <v>231</v>
       </c>
       <c r="H11" t="n">
-        <v>10.58</v>
+        <v>5.5</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J11" t="n">
-        <v>80000</v>
+        <v>13870</v>
       </c>
       <c r="K11" t="n">
-        <v>82900</v>
+        <v>14070</v>
       </c>
       <c r="L11" t="n">
-        <v>83000</v>
+        <v>14790</v>
       </c>
       <c r="M11" t="n">
-        <v>75300</v>
+        <v>13760</v>
       </c>
       <c r="N11" t="n">
-        <v>10.68</v>
+        <v>4.92</v>
       </c>
       <c r="O11" t="n">
-        <v>76416388500</v>
+        <v>52165126080</v>
       </c>
       <c r="P11" t="n">
-        <v>184000</v>
+        <v>30200</v>
       </c>
       <c r="Q11" t="n">
-        <v>44750</v>
+        <v>3540</v>
       </c>
       <c r="R11" t="n">
-        <v>-324000</v>
+        <v>-179000</v>
       </c>
       <c r="S11" t="n">
-        <v>-60000</v>
+        <v>-3000</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>K-방산 관련 뉴스에 따른 기대감. 공매도 세력에 대한 불만 및 주가 상승 전망.</t>
+          <t>원전 관련 기대감 언급. 신한투자증권의 공매도 의혹 및 주가 하락에 대한 불만.</t>
         </is>
       </c>
       <c r="U11" t="inlineStr"/>
       <c r="V11" t="n">
-        <v>0.3</v>
+        <v>0.1</v>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>['K-방산', '드론', '공매도']</t>
+          <t>['원전', '신한투자증권', '공매도']</t>
         </is>
       </c>
       <c r="X11" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
@@ -1476,38 +1476,38 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>272210</t>
+          <t>032820</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>대한광통신</t>
+          <t>미투온</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>17730</v>
+        <v>4175</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>'-3.22%</t>
+          <t>'-1.07%</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>3.29</v>
+        <v>-0.22</v>
       </c>
       <c r="E12" t="n">
-        <v>159</v>
+        <v>66</v>
       </c>
       <c r="F12" t="n">
-        <v>112</v>
+        <v>39</v>
       </c>
       <c r="G12" t="n">
-        <v>690</v>
+        <v>166</v>
       </c>
       <c r="H12" t="n">
-        <v>7.9</v>
+        <v>0.33</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -1515,51 +1515,51 @@
         </is>
       </c>
       <c r="J12" t="n">
-        <v>18320</v>
+        <v>4220</v>
       </c>
       <c r="K12" t="n">
-        <v>18450</v>
+        <v>4220</v>
       </c>
       <c r="L12" t="n">
-        <v>18590</v>
+        <v>4415</v>
       </c>
       <c r="M12" t="n">
-        <v>17590</v>
+        <v>4125</v>
       </c>
       <c r="N12" t="n">
-        <v>4.61</v>
+        <v>0.55</v>
       </c>
       <c r="O12" t="n">
-        <v>154024438620</v>
+        <v>25224807927</v>
       </c>
       <c r="P12" t="n">
-        <v>31500</v>
+        <v>6480</v>
       </c>
       <c r="Q12" t="n">
-        <v>1272</v>
+        <v>1738</v>
       </c>
       <c r="R12" t="n">
-        <v>-916000</v>
+        <v>121000</v>
       </c>
       <c r="S12" t="n">
         <v>0</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>미국 시장 광통신주 급등 및 AI주 동반 상승. 기관 매수에 따른 긍정적 전망.</t>
+          <t>코인 관련주 및 미버스 급등 속 상대적 부진. 거래량 부족 및 재료 소멸 우려.</t>
         </is>
       </c>
       <c r="U12" t="inlineStr"/>
       <c r="V12" t="n">
-        <v>0.4</v>
+        <v>0.1</v>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>['광통신', 'AI주', '기관매수']</t>
+          <t>['코인관련주', '미버스', '거래량']</t>
         </is>
       </c>
       <c r="X12" t="n">
-        <v>19</v>
+        <v>4</v>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
@@ -1568,38 +1568,38 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>010170</t>
+          <t>201490</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>대우건설</t>
+          <t>한화시스템</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>18280</v>
+        <v>78900</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>'-3.33%</t>
+          <t>'-1.38%</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>0</v>
+        <v>-0.1</v>
       </c>
       <c r="E13" t="n">
-        <v>46</v>
+        <v>123</v>
       </c>
       <c r="F13" t="n">
-        <v>34</v>
+        <v>70</v>
       </c>
       <c r="G13" t="n">
-        <v>203</v>
+        <v>551</v>
       </c>
       <c r="H13" t="n">
-        <v>10.74</v>
+        <v>10.58</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -1607,38 +1607,38 @@
         </is>
       </c>
       <c r="J13" t="n">
-        <v>18910</v>
+        <v>80000</v>
       </c>
       <c r="K13" t="n">
-        <v>19050</v>
+        <v>82900</v>
       </c>
       <c r="L13" t="n">
-        <v>19050</v>
+        <v>83000</v>
       </c>
       <c r="M13" t="n">
-        <v>18090</v>
+        <v>75300</v>
       </c>
       <c r="N13" t="n">
-        <v>10.74</v>
+        <v>10.68</v>
       </c>
       <c r="O13" t="n">
-        <v>48316449760</v>
+        <v>78680055100</v>
       </c>
       <c r="P13" t="n">
-        <v>40350</v>
+        <v>184000</v>
       </c>
       <c r="Q13" t="n">
-        <v>3320</v>
+        <v>44750</v>
       </c>
       <c r="R13" t="n">
-        <v>-331000</v>
+        <v>-324000</v>
       </c>
       <c r="S13" t="n">
-        <v>-47000</v>
+        <v>-60000</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>공매도 관련 논란 및 대차해지 운동 동참 요구. 주가 하락 추세에 대한 불만.</t>
+          <t>한화시스템, K-방산 관련 드론 시장 확대 기대감 및 10만 원대 돌파 전망. 공매도 세력 약화 및 숏커버링 가능성 언급. 뉴스 기반 긍정적 전망에도 불구하고 삼프로 TV 언급 후 주가 하락 및 시스템 조작 의혹 제기.</t>
         </is>
       </c>
       <c r="U13" t="inlineStr"/>
@@ -1647,11 +1647,11 @@
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>['공매도', '대차해지']</t>
+          <t>['K-방산', '드론', '공매도']</t>
         </is>
       </c>
       <c r="X13" t="n">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
@@ -1660,38 +1660,38 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>047040</t>
+          <t>272210</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>대한전선</t>
+          <t>대우건설</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>30350</v>
+        <v>18260</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>'-3.50%</t>
+          <t>'-3.44%</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>0.48</v>
+        <v>0</v>
       </c>
       <c r="E14" t="n">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="F14" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G14" t="n">
-        <v>106</v>
+        <v>205</v>
       </c>
       <c r="H14" t="n">
-        <v>11.92</v>
+        <v>10.74</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -1699,51 +1699,51 @@
         </is>
       </c>
       <c r="J14" t="n">
-        <v>31450</v>
+        <v>18910</v>
       </c>
       <c r="K14" t="n">
-        <v>31500</v>
+        <v>19050</v>
       </c>
       <c r="L14" t="n">
-        <v>31550</v>
+        <v>19050</v>
       </c>
       <c r="M14" t="n">
-        <v>29950</v>
+        <v>18090</v>
       </c>
       <c r="N14" t="n">
-        <v>11.44</v>
+        <v>10.74</v>
       </c>
       <c r="O14" t="n">
-        <v>56285610850</v>
+        <v>49445536600</v>
       </c>
       <c r="P14" t="n">
-        <v>75900</v>
+        <v>40350</v>
       </c>
       <c r="Q14" t="n">
-        <v>15000</v>
+        <v>3320</v>
       </c>
       <c r="R14" t="n">
-        <v>-166000</v>
+        <v>-331000</v>
       </c>
       <c r="S14" t="n">
-        <v>-8000</v>
+        <v>-47000</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>개인 투자자의 대한전선 매도 및 전선주 하락세 언급. 수급 불균형 우려.</t>
+          <t>공매도 관련 논란 및 대차해지 운동 동참 요구. 주가 하락 추세에 대한 불만.</t>
         </is>
       </c>
       <c r="U14" t="inlineStr"/>
       <c r="V14" t="n">
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>['전선주', '매도', '수급']</t>
+          <t>['공매도', '대차해지']</t>
         </is>
       </c>
       <c r="X14" t="n">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="Y14" t="inlineStr">
         <is>
@@ -1752,90 +1752,90 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>001440</t>
+          <t>047040</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>가온전선</t>
+          <t>대한광통신</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>311000</v>
+        <v>17690</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>'-4.89%</t>
+          <t>'-3.44%</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>1.66</v>
+        <v>3.29</v>
       </c>
       <c r="E15" t="n">
-        <v>95</v>
+        <v>163</v>
       </c>
       <c r="F15" t="n">
-        <v>70</v>
+        <v>112</v>
       </c>
       <c r="G15" t="n">
-        <v>186</v>
+        <v>708</v>
       </c>
       <c r="H15" t="n">
-        <v>3.62</v>
+        <v>7.9</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J15" t="n">
-        <v>327000</v>
+        <v>18320</v>
       </c>
       <c r="K15" t="n">
-        <v>324000</v>
+        <v>18450</v>
       </c>
       <c r="L15" t="n">
-        <v>340500</v>
+        <v>18590</v>
       </c>
       <c r="M15" t="n">
-        <v>308500</v>
+        <v>17590</v>
       </c>
       <c r="N15" t="n">
-        <v>1.96</v>
+        <v>4.61</v>
       </c>
       <c r="O15" t="n">
-        <v>65868693500</v>
+        <v>158532433785</v>
       </c>
       <c r="P15" t="n">
-        <v>635000</v>
+        <v>31500</v>
       </c>
       <c r="Q15" t="n">
-        <v>52600</v>
+        <v>1272</v>
       </c>
       <c r="R15" t="n">
-        <v>-24000</v>
+        <v>-916000</v>
       </c>
       <c r="S15" t="n">
-        <v>-2000</v>
+        <v>0</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>4381억 공급 계약 언급. 긍정적 조정 구간으로 해석. 신한증권에 대한 부정적 언급.</t>
+          <t>미국 광통신 AI 주가 급등 및 국내 관련주 동반 상승 기대. 기관 투자자들의 매수세 유입 및 연말·연초까지의 상승 전망 제시. 일부 투자자들의 매도 압력 및 급격한 가격 변동성 주의 필요.</t>
         </is>
       </c>
       <c r="U15" t="inlineStr"/>
       <c r="V15" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>['공급계약', '조정구간', '신한증권']</t>
+          <t>['광통신', 'AI', '기관매수']</t>
         </is>
       </c>
       <c r="X15" t="n">
-        <v>1</v>
+        <v>19</v>
       </c>
       <c r="Y15" t="inlineStr">
         <is>
@@ -1844,97 +1844,281 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>000500</t>
+          <t>010170</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>오름테라퓨틱</t>
+          <t>대한전선</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>27750</v>
+        <v>30300</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>'-25.80%</t>
+          <t>'-3.66%</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>0.01</v>
+        <v>0.48</v>
       </c>
       <c r="E16" t="n">
-        <v>510</v>
+        <v>57</v>
       </c>
       <c r="F16" t="n">
-        <v>283</v>
+        <v>36</v>
       </c>
       <c r="G16" t="n">
-        <v>936</v>
+        <v>107</v>
       </c>
       <c r="H16" t="n">
-        <v>7.09</v>
+        <v>11.92</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J16" t="n">
-        <v>37400</v>
+        <v>31450</v>
       </c>
       <c r="K16" t="n">
-        <v>26450</v>
+        <v>31500</v>
       </c>
       <c r="L16" t="n">
-        <v>28200</v>
+        <v>31550</v>
       </c>
       <c r="M16" t="n">
-        <v>26200</v>
+        <v>29950</v>
       </c>
       <c r="N16" t="n">
-        <v>7.08</v>
+        <v>11.44</v>
       </c>
       <c r="O16" t="n">
-        <v>65600722100</v>
+        <v>57622999500</v>
       </c>
       <c r="P16" t="n">
-        <v>146600</v>
+        <v>75900</v>
       </c>
       <c r="Q16" t="n">
-        <v>26200</v>
+        <v>15000</v>
       </c>
       <c r="R16" t="n">
-        <v>143000</v>
+        <v>-166000</v>
       </c>
       <c r="S16" t="n">
-        <v>42000</v>
+        <v>-8000</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>임상 진행 관련 불확실성 및 연속 하한가 발생. 투자자들의 신중한 접근 요구.</t>
+          <t>개인 투자자의 대한전선 매도 및 전선주 하락세 언급. 수급 불균형 우려.</t>
         </is>
       </c>
       <c r="U16" t="inlineStr"/>
       <c r="V16" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>['전선주', '매도', '수급']</t>
+        </is>
+      </c>
+      <c r="X16" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>활성</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>001440</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>가온전선</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>313500</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>'-4.13%</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="E17" t="n">
+        <v>101</v>
+      </c>
+      <c r="F17" t="n">
+        <v>72</v>
+      </c>
+      <c r="G17" t="n">
+        <v>188</v>
+      </c>
+      <c r="H17" t="n">
+        <v>3.62</v>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>MarketType.KOSPI</t>
+        </is>
+      </c>
+      <c r="J17" t="n">
+        <v>327000</v>
+      </c>
+      <c r="K17" t="n">
+        <v>324000</v>
+      </c>
+      <c r="L17" t="n">
+        <v>340500</v>
+      </c>
+      <c r="M17" t="n">
+        <v>308500</v>
+      </c>
+      <c r="N17" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="O17" t="n">
+        <v>66901423000</v>
+      </c>
+      <c r="P17" t="n">
+        <v>635000</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>52600</v>
+      </c>
+      <c r="R17" t="n">
+        <v>-24000</v>
+      </c>
+      <c r="S17" t="n">
+        <v>-2000</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>가온전선, 40만 원 이상 상승 전망에도 불구하고 차익 실현 매물 출현 및 주가 하락. 신한증권 이용자들의 불만 제기 및 주가 고평가 논란. 조정 구간에서의 신중한 접근 필요.</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr"/>
+      <c r="V17" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>['조정', '신한증권', '고평가']</t>
+        </is>
+      </c>
+      <c r="X17" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>활성</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>000500</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>오름테라퓨틱</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>27600</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>'-26.20%</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E18" t="n">
+        <v>529</v>
+      </c>
+      <c r="F18" t="n">
+        <v>294</v>
+      </c>
+      <c r="G18" t="n">
+        <v>959</v>
+      </c>
+      <c r="H18" t="n">
+        <v>7.09</v>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>MarketType.KOSDAQ</t>
+        </is>
+      </c>
+      <c r="J18" t="n">
+        <v>37400</v>
+      </c>
+      <c r="K18" t="n">
+        <v>26450</v>
+      </c>
+      <c r="L18" t="n">
+        <v>28200</v>
+      </c>
+      <c r="M18" t="n">
+        <v>26200</v>
+      </c>
+      <c r="N18" t="n">
+        <v>7.08</v>
+      </c>
+      <c r="O18" t="n">
+        <v>67556364550</v>
+      </c>
+      <c r="P18" t="n">
+        <v>146600</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>26200</v>
+      </c>
+      <c r="R18" t="n">
+        <v>143000</v>
+      </c>
+      <c r="S18" t="n">
+        <v>42000</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>임상 진행 관련 불확실성 및 연속 하한가 발생. 투자자들의 신중한 접근 요구.</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr"/>
+      <c r="V18" t="n">
         <v>0.2</v>
       </c>
-      <c r="W16" t="inlineStr">
+      <c r="W18" t="inlineStr">
         <is>
           <t>['임상', '하한가', '바이오']</t>
         </is>
       </c>
-      <c r="X16" t="n">
+      <c r="X18" t="n">
         <v>1</v>
       </c>
-      <c r="Y16" t="inlineStr">
+      <c r="Y18" t="inlineStr">
         <is>
           <t>활성</t>
         </is>
       </c>
-      <c r="Z16" t="inlineStr">
+      <c r="Z18" t="inlineStr">
         <is>
           <t>475830</t>
         </is>

--- a/data/trending_integrated_20260921_10.xlsx
+++ b/data/trending_integrated_20260921_10.xlsx
@@ -567,24 +567,24 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>24050</v>
+        <v>25250</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>'+23.71%</t>
+          <t>'+29.89%</t>
         </is>
       </c>
       <c r="D2" t="n">
         <v>-0.04</v>
       </c>
       <c r="E2" t="n">
-        <v>96</v>
+        <v>120</v>
       </c>
       <c r="F2" t="n">
-        <v>75</v>
+        <v>84</v>
       </c>
       <c r="G2" t="n">
-        <v>167</v>
+        <v>205</v>
       </c>
       <c r="H2" t="n">
         <v>0.35</v>
@@ -601,7 +601,7 @@
         <v>20200</v>
       </c>
       <c r="L2" t="n">
-        <v>24150</v>
+        <v>25250</v>
       </c>
       <c r="M2" t="n">
         <v>19610</v>
@@ -610,7 +610,7 @@
         <v>0.39</v>
       </c>
       <c r="O2" t="n">
-        <v>160650885860</v>
+        <v>190563497535</v>
       </c>
       <c r="P2" t="n">
         <v>39350</v>
@@ -626,16 +626,16 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>스카이랩스, 美 타임 선정 '세계 최고 헬스테크 기업' 그룹 선정 소식에 주가 급등. 2주간의 하락 후 반등하며 세계적 인정에 대한 기대감 고조. 기관 및 외국인 프로그램 매수세 유입, 9%대 상승 기록.</t>
+          <t>스카이랩스, 美 타임지 선정 '세계 최고 헬스테크 기업'으로 부각. 단기 반등 후 급등 기대감 형성.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>['헬스테크', '타임지', '기관외국인']</t>
+          <t>['헬스테크', '타임지', '급등']</t>
         </is>
       </c>
       <c r="X2" t="n">
@@ -659,24 +659,24 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>10740</v>
+        <v>10930</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+19.07%</t>
+          <t>'+21.18%</t>
         </is>
       </c>
       <c r="D3" t="n">
         <v>0.09</v>
       </c>
       <c r="E3" t="n">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="F3" t="n">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="G3" t="n">
-        <v>95</v>
+        <v>109</v>
       </c>
       <c r="H3" t="n">
         <v>8.6</v>
@@ -693,7 +693,7 @@
         <v>9050</v>
       </c>
       <c r="L3" t="n">
-        <v>10910</v>
+        <v>10940</v>
       </c>
       <c r="M3" t="n">
         <v>9010</v>
@@ -702,7 +702,7 @@
         <v>8.51</v>
       </c>
       <c r="O3" t="n">
-        <v>149619179155</v>
+        <v>159367403810</v>
       </c>
       <c r="P3" t="n">
         <v>11640</v>
@@ -718,7 +718,7 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>SFA반도체, 삼성전자와의 대규모 공급 계약 체결 소식에 급등. 후공정 대장주로서의 입지 강화 및 4000원 돌파 후 전고점 돌파 기대감 고조. 15000원 목표가 제시 및 상승 추세 지속 가능성 언급.</t>
+          <t>SFA반도체, 후공정 대장주로서 급등세. 전고점 돌파 및 15,000원 목표가 제시. 공매도 숏커버 기대.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
@@ -727,7 +727,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>['공급계약', '후공정', '추세']</t>
+          <t>['후공정', '급등', '목표가']</t>
         </is>
       </c>
       <c r="X3" t="n">
@@ -751,24 +751,24 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>5925</v>
+        <v>5860</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+9.12%</t>
+          <t>'+7.92%</t>
         </is>
       </c>
       <c r="D4" t="n">
         <v>-0.31</v>
       </c>
       <c r="E4" t="n">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="F4" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="G4" t="n">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="H4" t="n">
         <v>0.19</v>
@@ -794,7 +794,7 @@
         <v>0.5</v>
       </c>
       <c r="O4" t="n">
-        <v>54016565995</v>
+        <v>55718626405</v>
       </c>
       <c r="P4" t="n">
         <v>13140</v>
@@ -839,83 +839,83 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>HLB</t>
+          <t>광전자</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>31500</v>
+        <v>11120</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+6.24%</t>
+          <t>'+5.70%</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>-0.48</v>
+        <v>0.16</v>
       </c>
       <c r="E5" t="n">
-        <v>236</v>
+        <v>73</v>
       </c>
       <c r="F5" t="n">
-        <v>165</v>
+        <v>52</v>
       </c>
       <c r="G5" t="n">
-        <v>962</v>
+        <v>137</v>
       </c>
       <c r="H5" t="n">
-        <v>16.67</v>
+        <v>18.29</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J5" t="n">
-        <v>29650</v>
+        <v>10520</v>
       </c>
       <c r="K5" t="n">
-        <v>30400</v>
+        <v>10780</v>
       </c>
       <c r="L5" t="n">
-        <v>33400</v>
+        <v>12190</v>
       </c>
       <c r="M5" t="n">
-        <v>29400</v>
+        <v>10590</v>
       </c>
       <c r="N5" t="n">
-        <v>17.15</v>
+        <v>18.13</v>
       </c>
       <c r="O5" t="n">
-        <v>20664938425</v>
+        <v>159846090110</v>
       </c>
       <c r="P5" t="n">
-        <v>69200</v>
+        <v>22450</v>
       </c>
       <c r="Q5" t="n">
-        <v>24150</v>
+        <v>1760</v>
       </c>
       <c r="R5" t="n">
-        <v>-37000</v>
+        <v>-18000</v>
       </c>
       <c r="S5" t="n">
-        <v>-1000</v>
+        <v>0</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>FDA 승인 관련 기대와 불확실성 혼재. 임상 성공 여부 및 주가 패턴에 대한 논쟁.</t>
+          <t>미국 광통신주 급등에 영향을 받으며 국내 증시도 동반 상승 기대. 그러나 개인 투자자들의 매도 심리 및 차익 실현 매물 출현 가능성으로 단기적인 조정 우려. 높은 변동성 속 신중한 접근 필요.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['FDA승인', '임상성공', '주가패턴']</t>
+          <t>['광통신', '추세', '변동성']</t>
         </is>
       </c>
       <c r="X5" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
@@ -924,77 +924,77 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>028300</t>
+          <t>017900</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>삼성전자우</t>
+          <t>HLB</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>207500</v>
+        <v>31300</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'+5.81%</t>
+          <t>'+5.56%</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>-0.09</v>
+        <v>-0.48</v>
       </c>
       <c r="E6" t="n">
-        <v>46</v>
+        <v>270</v>
       </c>
       <c r="F6" t="n">
-        <v>38</v>
+        <v>176</v>
       </c>
       <c r="G6" t="n">
-        <v>199</v>
+        <v>1125</v>
       </c>
       <c r="H6" t="n">
-        <v>75.44</v>
+        <v>16.67</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J6" t="n">
-        <v>196100</v>
+        <v>29650</v>
       </c>
       <c r="K6" t="n">
-        <v>199800</v>
+        <v>30400</v>
       </c>
       <c r="L6" t="n">
-        <v>207500</v>
+        <v>33400</v>
       </c>
       <c r="M6" t="n">
-        <v>199600</v>
+        <v>29400</v>
       </c>
       <c r="N6" t="n">
-        <v>75.53</v>
+        <v>17.15</v>
       </c>
       <c r="O6" t="n">
-        <v>431361341300</v>
+        <v>21613853500</v>
       </c>
       <c r="P6" t="n">
-        <v>243500</v>
+        <v>69200</v>
       </c>
       <c r="Q6" t="n">
-        <v>64700</v>
+        <v>24150</v>
       </c>
       <c r="R6" t="n">
-        <v>398000</v>
+        <v>-37000</v>
       </c>
       <c r="S6" t="n">
-        <v>-36000</v>
+        <v>-1000</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>삼성전자 우선주, 배당 기대감과 자사주 취득 소각 뉴스에 힘입어 강세 전망. 본주 매입 완료 후 물량 풀릴 가능성 및 배당락 영향에 대한 상반된 의견 존재. 20만 원대 매수 후 장기 보유 전략 제시.</t>
+          <t>HLB, 담관암 신약 승인 관련 불확실성 속 주가 급락. FDA 승인 및 임상 성공 여부 논란.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
@@ -1003,7 +1003,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['배당', '자사주', '전망']</t>
+          <t>['신약승인', '담관암', 'FDA']</t>
         </is>
       </c>
       <c r="X6" t="n">
@@ -1016,38 +1016,38 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>005935</t>
+          <t>028300</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>광전자</t>
+          <t>삼성전자우</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>11090</v>
+        <v>207000</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'+5.42%</t>
+          <t>'+5.56%</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>0.16</v>
+        <v>-0.09</v>
       </c>
       <c r="E7" t="n">
-        <v>70</v>
+        <v>53</v>
       </c>
       <c r="F7" t="n">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="G7" t="n">
-        <v>135</v>
+        <v>224</v>
       </c>
       <c r="H7" t="n">
-        <v>18.29</v>
+        <v>75.44</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -1055,51 +1055,51 @@
         </is>
       </c>
       <c r="J7" t="n">
-        <v>10520</v>
+        <v>196100</v>
       </c>
       <c r="K7" t="n">
-        <v>10780</v>
+        <v>199800</v>
       </c>
       <c r="L7" t="n">
-        <v>12190</v>
+        <v>207500</v>
       </c>
       <c r="M7" t="n">
-        <v>10590</v>
+        <v>199600</v>
       </c>
       <c r="N7" t="n">
-        <v>18.13</v>
+        <v>75.53</v>
       </c>
       <c r="O7" t="n">
-        <v>158705410680</v>
+        <v>442803942300</v>
       </c>
       <c r="P7" t="n">
-        <v>22450</v>
+        <v>243500</v>
       </c>
       <c r="Q7" t="n">
-        <v>1760</v>
+        <v>64700</v>
       </c>
       <c r="R7" t="n">
-        <v>-18000</v>
+        <v>398000</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>-36000</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>미국 광통신주 급등에 영향을 받으며 국내 증시도 동반 상승 기대. 그러나 개인 투자자들의 매도 심리 및 차익 실현 매물 출현 가능성으로 단기적인 조정 우려. 높은 변동성 속 신중한 접근 필요.</t>
+          <t>삼성전자우, 배당 기대감 속 주가 상승 전망. 자사주 취득 및 소각, 외인 매수세 유입 가능성 언급.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['광통신', '추세', '변동성']</t>
+          <t>['배당', '자사주', '외인']</t>
         </is>
       </c>
       <c r="X7" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
@@ -1108,7 +1108,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>017900</t>
+          <t>005935</t>
         </is>
       </c>
     </row>
@@ -1130,13 +1130,13 @@
         <v>-0.02</v>
       </c>
       <c r="E8" t="n">
-        <v>717</v>
+        <v>746</v>
       </c>
       <c r="F8" t="n">
-        <v>453</v>
+        <v>472</v>
       </c>
       <c r="G8" t="n">
-        <v>2945</v>
+        <v>3115</v>
       </c>
       <c r="H8" t="n">
         <v>46.46</v>
@@ -1153,7 +1153,7 @@
         <v>264000</v>
       </c>
       <c r="L8" t="n">
-        <v>272000</v>
+        <v>272500</v>
       </c>
       <c r="M8" t="n">
         <v>263500</v>
@@ -1162,7 +1162,7 @@
         <v>46.48</v>
       </c>
       <c r="O8" t="n">
-        <v>2318122482000</v>
+        <v>2476012877250</v>
       </c>
       <c r="P8" t="n">
         <v>374500</v>
@@ -1178,12 +1178,12 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>내년 상반기까지 상승장 기대감 속 삼성전자 주가 상승 전망. AI 감속론은 부정적 전망으로 작용할 수 있으나, 배당 효과 및 경쟁사 주가 상승이 긍정적 요인으로 작용. 증권사 시스템 장애 이슈는 단기적 투자 심리에 영향.</t>
+          <t>삼성전자, 내년 상반기 상승장 전망 속 일부 증권사 앱 먹통 문제 발생. 배당 및 AI 감속론 관련 언급.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="W8" t="inlineStr">
         <is>
@@ -1211,24 +1211,24 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1878000</v>
+        <v>1872000</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>'+1.13%</t>
+          <t>'+0.81%</t>
         </is>
       </c>
       <c r="D9" t="n">
         <v>0.13</v>
       </c>
       <c r="E9" t="n">
-        <v>748</v>
+        <v>767</v>
       </c>
       <c r="F9" t="n">
-        <v>444</v>
+        <v>452</v>
       </c>
       <c r="G9" t="n">
-        <v>2872</v>
+        <v>2956</v>
       </c>
       <c r="H9" t="n">
         <v>50.23</v>
@@ -1254,7 +1254,7 @@
         <v>50.1</v>
       </c>
       <c r="O9" t="n">
-        <v>1969961380000</v>
+        <v>2101075311000</v>
       </c>
       <c r="P9" t="n">
         <v>2987000</v>
@@ -1303,11 +1303,11 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>26900</v>
+        <v>27000</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'+0.37%</t>
+          <t>'+0.75%</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -1320,7 +1320,7 @@
         <v>32</v>
       </c>
       <c r="G10" t="n">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="H10" t="n">
         <v>2.11</v>
@@ -1346,7 +1346,7 @@
         <v>2.41</v>
       </c>
       <c r="O10" t="n">
-        <v>95160757725</v>
+        <v>96623250600</v>
       </c>
       <c r="P10" t="n">
         <v>59600</v>
@@ -1362,16 +1362,16 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>성호전자, 3일간의 폭등 후 차익 실현 매물 출현 가능성 언급. 외인·기관 쌍끌이 매수세 유입 및 10만 원 이상 상승 가능성 제시. 자회사 상장 반대 등 잠재적 리스크 요인 존재.</t>
+          <t>성호전자, 미국 광통신 AI주 동반 상승 및 외인/기관 매수세 유입. 3만원 목표가 제시 및 투경 관련 논의.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>['폭등', '외인기관', '상승가능성']</t>
+          <t>['AI', '광통신', '목표가']</t>
         </is>
       </c>
       <c r="X10" t="n">
@@ -1395,24 +1395,24 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>13800</v>
+        <v>13740</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>'-0.50%</t>
+          <t>'-0.94%</t>
         </is>
       </c>
       <c r="D11" t="n">
         <v>0.58</v>
       </c>
       <c r="E11" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F11" t="n">
         <v>26</v>
       </c>
       <c r="G11" t="n">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="H11" t="n">
         <v>5.5</v>
@@ -1432,13 +1432,13 @@
         <v>14790</v>
       </c>
       <c r="M11" t="n">
-        <v>13760</v>
+        <v>13730</v>
       </c>
       <c r="N11" t="n">
         <v>4.92</v>
       </c>
       <c r="O11" t="n">
-        <v>52165126080</v>
+        <v>53970419700</v>
       </c>
       <c r="P11" t="n">
         <v>30200</v>
@@ -1487,24 +1487,24 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>4175</v>
+        <v>4165</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>'-1.07%</t>
+          <t>'-1.30%</t>
         </is>
       </c>
       <c r="D12" t="n">
         <v>-0.22</v>
       </c>
       <c r="E12" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="F12" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="G12" t="n">
-        <v>166</v>
+        <v>180</v>
       </c>
       <c r="H12" t="n">
         <v>0.33</v>
@@ -1530,7 +1530,7 @@
         <v>0.55</v>
       </c>
       <c r="O12" t="n">
-        <v>25224807927</v>
+        <v>25555202920</v>
       </c>
       <c r="P12" t="n">
         <v>6480</v>
@@ -1546,7 +1546,7 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>코인 관련주 및 미버스 급등 속 상대적 부진. 거래량 부족 및 재료 소멸 우려.</t>
+          <t>미투온, 미버스 관련 코인주 동반 상승 속 거래량 부진 및 재료 소멸 우려. 매도 물량 출회 가능성.</t>
         </is>
       </c>
       <c r="U12" t="inlineStr"/>
@@ -1555,7 +1555,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>['코인관련주', '미버스', '거래량']</t>
+          <t>['미버스', '거래량', '재료소멸']</t>
         </is>
       </c>
       <c r="X12" t="n">
@@ -1579,24 +1579,24 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>78900</v>
+        <v>78800</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>'-1.38%</t>
+          <t>'-1.50%</t>
         </is>
       </c>
       <c r="D13" t="n">
         <v>-0.1</v>
       </c>
       <c r="E13" t="n">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="F13" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G13" t="n">
-        <v>551</v>
+        <v>568</v>
       </c>
       <c r="H13" t="n">
         <v>10.58</v>
@@ -1622,7 +1622,7 @@
         <v>10.68</v>
       </c>
       <c r="O13" t="n">
-        <v>78680055100</v>
+        <v>80534159400</v>
       </c>
       <c r="P13" t="n">
         <v>184000</v>
@@ -1671,24 +1671,24 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>18260</v>
+        <v>18230</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>'-3.44%</t>
+          <t>'-1.99%</t>
         </is>
       </c>
       <c r="D14" t="n">
         <v>0</v>
       </c>
       <c r="E14" t="n">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="F14" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G14" t="n">
-        <v>205</v>
+        <v>226</v>
       </c>
       <c r="H14" t="n">
         <v>10.74</v>
@@ -1699,28 +1699,28 @@
         </is>
       </c>
       <c r="J14" t="n">
-        <v>18910</v>
+        <v>18600</v>
       </c>
       <c r="K14" t="n">
-        <v>19050</v>
+        <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>19050</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>18090</v>
+        <v>0</v>
       </c>
       <c r="N14" t="n">
         <v>10.74</v>
       </c>
       <c r="O14" t="n">
-        <v>49445536600</v>
+        <v>51030000000</v>
       </c>
       <c r="P14" t="n">
-        <v>40350</v>
+        <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>3320</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
         <v>-331000</v>
@@ -1730,16 +1730,16 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>공매도 관련 논란 및 대차해지 운동 동참 요구. 주가 하락 추세에 대한 불만.</t>
+          <t>대우건설, 공매도 장부 조작 의혹 및 대차해지 운동 동참 호소. 주가 하락 추세 및 기관 매매 관련 논의.</t>
         </is>
       </c>
       <c r="U14" t="inlineStr"/>
       <c r="V14" t="n">
-        <v>0.3</v>
+        <v>0.1</v>
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>['공매도', '대차해지']</t>
+          <t>['공매도', '대차해지', '추세']</t>
         </is>
       </c>
       <c r="X14" t="n">
@@ -1763,24 +1763,24 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>17690</v>
+        <v>17630</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>'-3.44%</t>
+          <t>'-3.77%</t>
         </is>
       </c>
       <c r="D15" t="n">
         <v>3.29</v>
       </c>
       <c r="E15" t="n">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c r="F15" t="n">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="G15" t="n">
-        <v>708</v>
+        <v>712</v>
       </c>
       <c r="H15" t="n">
         <v>7.9</v>
@@ -1806,7 +1806,7 @@
         <v>4.61</v>
       </c>
       <c r="O15" t="n">
-        <v>158532433785</v>
+        <v>163238188460</v>
       </c>
       <c r="P15" t="n">
         <v>31500</v>
@@ -1855,11 +1855,11 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>30300</v>
+        <v>30250</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>'-3.66%</t>
+          <t>'-3.82%</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -1872,7 +1872,7 @@
         <v>36</v>
       </c>
       <c r="G16" t="n">
-        <v>107</v>
+        <v>120</v>
       </c>
       <c r="H16" t="n">
         <v>11.92</v>
@@ -1898,7 +1898,7 @@
         <v>11.44</v>
       </c>
       <c r="O16" t="n">
-        <v>57622999500</v>
+        <v>59148181550</v>
       </c>
       <c r="P16" t="n">
         <v>75900</v>
@@ -1914,7 +1914,7 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>개인 투자자의 대한전선 매도 및 전선주 하락세 언급. 수급 불균형 우려.</t>
+          <t>대한전선, 금일 하락세 속 반도체 소부장 순환매 관련 언급. 장기 이평선 저항 및 매물대 관련 논의.</t>
         </is>
       </c>
       <c r="U16" t="inlineStr"/>
@@ -1923,7 +1923,7 @@
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>['전선주', '매도', '수급']</t>
+          <t>['하락', '순환매', '매물대']</t>
         </is>
       </c>
       <c r="X16" t="n">
@@ -1947,24 +1947,24 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>313500</v>
+        <v>314500</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>'-4.13%</t>
+          <t>'-3.82%</t>
         </is>
       </c>
       <c r="D17" t="n">
         <v>1.66</v>
       </c>
       <c r="E17" t="n">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="F17" t="n">
         <v>72</v>
       </c>
       <c r="G17" t="n">
-        <v>188</v>
+        <v>200</v>
       </c>
       <c r="H17" t="n">
         <v>3.62</v>
@@ -1990,7 +1990,7 @@
         <v>1.96</v>
       </c>
       <c r="O17" t="n">
-        <v>66901423000</v>
+        <v>68272832500</v>
       </c>
       <c r="P17" t="n">
         <v>635000</v>
@@ -2006,16 +2006,16 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>가온전선, 40만 원 이상 상승 전망에도 불구하고 차익 실현 매물 출현 및 주가 하락. 신한증권 이용자들의 불만 제기 및 주가 고평가 논란. 조정 구간에서의 신중한 접근 필요.</t>
+          <t>가온전선, 금일 하락세 속 40만원 이상 돌파 전망. 외국인 매도 물량 출회 및 고평가 논란.</t>
         </is>
       </c>
       <c r="U17" t="inlineStr"/>
       <c r="V17" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>['조정', '신한증권', '고평가']</t>
+          <t>['하락', '돌파', '고평가']</t>
         </is>
       </c>
       <c r="X17" t="n">
@@ -2039,24 +2039,24 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>27600</v>
+        <v>27100</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>'-26.20%</t>
+          <t>'-23.66%</t>
         </is>
       </c>
       <c r="D18" t="n">
         <v>0.01</v>
       </c>
       <c r="E18" t="n">
-        <v>529</v>
+        <v>542</v>
       </c>
       <c r="F18" t="n">
-        <v>294</v>
+        <v>299</v>
       </c>
       <c r="G18" t="n">
-        <v>959</v>
+        <v>1015</v>
       </c>
       <c r="H18" t="n">
         <v>7.09</v>
@@ -2067,28 +2067,28 @@
         </is>
       </c>
       <c r="J18" t="n">
-        <v>37400</v>
+        <v>35500</v>
       </c>
       <c r="K18" t="n">
-        <v>26450</v>
+        <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>28200</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>26200</v>
+        <v>0</v>
       </c>
       <c r="N18" t="n">
         <v>7.08</v>
       </c>
       <c r="O18" t="n">
-        <v>67556364550</v>
+        <v>68862000000</v>
       </c>
       <c r="P18" t="n">
-        <v>146600</v>
+        <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>26200</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
         <v>143000</v>
